--- a/doc/5、开发文档/DFDL33-SH8619 协议转换单元DLT64点表.xlsx
+++ b/doc/5、开发文档/DFDL33-SH8619 协议转换单元DLT64点表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Project\SVN\DFDL33-SH8619\doc\5、开发文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B2D4D8E-6139-4B8F-84E5-19A39F194E85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A625E593-6DAD-4DE5-9649-4B393DE2376E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="2775" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="217">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="219">
   <si>
     <t>00</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -880,6 +880,14 @@
   </si>
   <si>
     <t>厂家软件版本号(ASCII 码)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>电压校准</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>电源接入220V，写1进行电压校准</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1114,16 +1122,37 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1133,55 +1162,34 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1514,7 +1522,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D2C9C05F-D0FC-4B32-8A10-0D5248EE0CE7}">
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="9" style="23"/>
@@ -1542,26 +1550,26 @@
       <c r="K1" s="13"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="29" t="s">
+      <c r="A2" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
       <c r="E2" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="42" t="s">
+      <c r="F2" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="G2" s="35" t="s">
+      <c r="G2" s="37" t="s">
         <v>137</v>
       </c>
       <c r="H2" s="30" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="30"/>
-      <c r="J2" s="44" t="s">
+      <c r="J2" s="39" t="s">
         <v>5</v>
       </c>
       <c r="K2" s="31" t="s">
@@ -1582,34 +1590,34 @@
         <v>9</v>
       </c>
       <c r="E3" s="30"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="43"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="38"/>
       <c r="H3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="44"/>
+      <c r="J3" s="39"/>
       <c r="K3" s="32"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="29" t="s">
+      <c r="A4" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="33" t="s">
         <v>184</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="49" t="s">
+      <c r="E4" s="36" t="s">
         <v>185</v>
       </c>
-      <c r="F4" s="42" t="s">
+      <c r="F4" s="34" t="s">
         <v>186</v>
       </c>
       <c r="G4" s="21"/>
@@ -1622,53 +1630,53 @@
       <c r="J4" s="1" t="s">
         <v>187</v>
       </c>
-      <c r="K4" s="50"/>
+      <c r="K4" s="29"/>
     </row>
     <row r="5" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="29"/>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
+      <c r="A5" s="33"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="33"/>
       <c r="D5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="49"/>
-      <c r="F5" s="42"/>
+      <c r="E5" s="36"/>
+      <c r="F5" s="34"/>
       <c r="G5" s="21"/>
       <c r="H5" s="30"/>
       <c r="I5" s="30"/>
       <c r="J5" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="K5" s="51" t="s">
+      <c r="K5" s="35" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="29"/>
-      <c r="B6" s="29"/>
-      <c r="C6" s="29"/>
+      <c r="A6" s="33"/>
+      <c r="B6" s="33"/>
+      <c r="C6" s="33"/>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="42"/>
+      <c r="E6" s="36"/>
+      <c r="F6" s="34"/>
       <c r="G6" s="21"/>
       <c r="H6" s="30"/>
       <c r="I6" s="30"/>
       <c r="J6" s="1" t="s">
         <v>189</v>
       </c>
-      <c r="K6" s="51"/>
+      <c r="K6" s="35"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="29"/>
-      <c r="B7" s="29"/>
-      <c r="C7" s="29"/>
+      <c r="A7" s="33"/>
+      <c r="B7" s="33"/>
+      <c r="C7" s="33"/>
       <c r="D7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="49"/>
-      <c r="F7" s="42"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="34"/>
       <c r="G7" s="21" t="s">
         <v>195</v>
       </c>
@@ -1677,17 +1685,17 @@
       <c r="J7" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="K7" s="51"/>
+      <c r="K7" s="35"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="29"/>
-      <c r="B8" s="29"/>
-      <c r="C8" s="29"/>
+      <c r="A8" s="33"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="33"/>
       <c r="D8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="49"/>
-      <c r="F8" s="42"/>
+      <c r="E8" s="36"/>
+      <c r="F8" s="34"/>
       <c r="G8" s="1" t="s">
         <v>196</v>
       </c>
@@ -1696,58 +1704,58 @@
       <c r="J8" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="K8" s="51"/>
+      <c r="K8" s="35"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="29"/>
-      <c r="B9" s="29"/>
-      <c r="C9" s="29"/>
+      <c r="A9" s="33"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
       <c r="D9" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="49"/>
-      <c r="F9" s="42"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="34"/>
       <c r="G9" s="1"/>
       <c r="H9" s="30"/>
       <c r="I9" s="30"/>
       <c r="J9" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="K9" s="51"/>
+      <c r="K9" s="35"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="29"/>
-      <c r="B10" s="29"/>
-      <c r="C10" s="29"/>
+      <c r="A10" s="33"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="33"/>
       <c r="D10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="49"/>
-      <c r="F10" s="42"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="34"/>
       <c r="G10" s="1"/>
       <c r="H10" s="30"/>
       <c r="I10" s="30"/>
       <c r="J10" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="K10" s="51"/>
+      <c r="K10" s="35"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="29"/>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
+      <c r="A11" s="33"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="33"/>
       <c r="D11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="49"/>
-      <c r="F11" s="42"/>
+      <c r="E11" s="36"/>
+      <c r="F11" s="34"/>
       <c r="G11" s="1"/>
       <c r="H11" s="30"/>
       <c r="I11" s="30"/>
       <c r="J11" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="K11" s="51"/>
+      <c r="K11" s="35"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="26" t="s">
@@ -1875,57 +1883,71 @@
         <v>213</v>
       </c>
     </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="29" t="s">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17" s="26" t="s">
+        <v>75</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>0</v>
+      </c>
+      <c r="E17" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="F17" s="27">
+        <v>1</v>
+      </c>
+      <c r="G17" s="27"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="J17" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="K17" s="28" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="29" t="s">
+      <c r="B19" s="33" t="s">
         <v>183</v>
       </c>
-      <c r="C18" s="29" t="s">
+      <c r="C19" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="29" t="s">
+      <c r="D19" s="33" t="s">
         <v>203</v>
       </c>
-      <c r="E18" s="27" t="s">
+      <c r="E19" s="27" t="s">
         <v>205</v>
-      </c>
-      <c r="F18" s="27"/>
-      <c r="G18" s="27"/>
-      <c r="H18" s="30" t="s">
-        <v>215</v>
-      </c>
-      <c r="I18" s="30" t="s">
-        <v>14</v>
-      </c>
-      <c r="J18" s="27" t="s">
-        <v>206</v>
-      </c>
-      <c r="K18" s="28"/>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="29"/>
-      <c r="B19" s="29"/>
-      <c r="C19" s="29"/>
-      <c r="D19" s="29"/>
-      <c r="E19" s="27" t="s">
-        <v>204</v>
       </c>
       <c r="F19" s="27"/>
       <c r="G19" s="27"/>
-      <c r="H19" s="30"/>
-      <c r="I19" s="30"/>
+      <c r="H19" s="30" t="s">
+        <v>215</v>
+      </c>
+      <c r="I19" s="30" t="s">
+        <v>14</v>
+      </c>
       <c r="J19" s="27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K19" s="28"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="29"/>
-      <c r="B20" s="29"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
+      <c r="A20" s="33"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="33"/>
       <c r="E20" s="27" t="s">
         <v>204</v>
       </c>
@@ -1934,42 +1956,64 @@
       <c r="H20" s="30"/>
       <c r="I20" s="30"/>
       <c r="J20" s="27" t="s">
+        <v>207</v>
+      </c>
+      <c r="K20" s="28"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="33"/>
+      <c r="B21" s="33"/>
+      <c r="C21" s="33"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="27" t="s">
+        <v>204</v>
+      </c>
+      <c r="F21" s="27"/>
+      <c r="G21" s="27"/>
+      <c r="H21" s="30"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="27" t="s">
         <v>208</v>
       </c>
-      <c r="K20" s="28"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="26" t="s">
+      <c r="K21" s="28"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="B22" s="26" t="s">
+      <c r="B23" s="26" t="s">
         <v>184</v>
       </c>
-      <c r="C22" s="26" t="s">
+      <c r="C23" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="D22" s="26" t="s">
+      <c r="D23" s="26" t="s">
         <v>23</v>
       </c>
-      <c r="E22" s="27" t="s">
+      <c r="E23" s="27" t="s">
         <v>214</v>
       </c>
-      <c r="F22" s="27">
+      <c r="F23" s="27">
         <v>32</v>
       </c>
-      <c r="G22" s="27"/>
-      <c r="H22" s="27" t="s">
+      <c r="G23" s="27"/>
+      <c r="H23" s="27" t="s">
         <v>215</v>
       </c>
-      <c r="I22" s="27"/>
-      <c r="J22" s="27" t="s">
+      <c r="I23" s="27"/>
+      <c r="J23" s="27" t="s">
         <v>216</v>
       </c>
-      <c r="K22" s="28"/>
+      <c r="K23" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="I18:I20"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="H19:H21"/>
+    <mergeCell ref="I19:I21"/>
     <mergeCell ref="K2:K3"/>
     <mergeCell ref="A4:A11"/>
     <mergeCell ref="B4:B11"/>
@@ -1985,14 +2029,9 @@
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="J2:J3"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="B18:B20"/>
-    <mergeCell ref="C18:C20"/>
-    <mergeCell ref="D18:D20"/>
-    <mergeCell ref="H18:H20"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A18:D18">
+  <conditionalFormatting sqref="A19:D19">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -2101,17 +2140,17 @@
       <c r="E2" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="F2" s="42" t="s">
+      <c r="F2" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="G2" s="35" t="s">
+      <c r="G2" s="37" t="s">
         <v>137</v>
       </c>
       <c r="H2" s="30" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="30"/>
-      <c r="J2" s="44" t="s">
+      <c r="J2" s="39" t="s">
         <v>5</v>
       </c>
       <c r="K2" s="31" t="s">
@@ -2132,25 +2171,25 @@
         <v>9</v>
       </c>
       <c r="E3" s="30"/>
-      <c r="F3" s="42"/>
-      <c r="G3" s="43"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="38"/>
       <c r="H3" s="1" t="s">
         <v>10</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J3" s="44"/>
+      <c r="J3" s="39"/>
       <c r="K3" s="32"/>
     </row>
     <row r="4" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="33" t="s">
+      <c r="A4" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="C4" s="40" t="s">
         <v>42</v>
       </c>
       <c r="D4" s="2" t="s">
@@ -2159,14 +2198,14 @@
       <c r="E4" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="F4" s="35" t="s">
+      <c r="F4" s="37" t="s">
         <v>45</v>
       </c>
       <c r="G4" s="9"/>
-      <c r="H4" s="37" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="37" t="s">
+      <c r="H4" s="42" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="42" t="s">
         <v>14</v>
       </c>
       <c r="J4" s="1" t="s">
@@ -2175,220 +2214,220 @@
       <c r="K4" s="12"/>
     </row>
     <row r="5" spans="1:11" ht="72" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="34"/>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
+      <c r="A5" s="41"/>
+      <c r="B5" s="41"/>
+      <c r="C5" s="41"/>
       <c r="D5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="40" t="s">
+      <c r="E5" s="48" t="s">
         <v>136</v>
       </c>
-      <c r="F5" s="36"/>
+      <c r="F5" s="44"/>
       <c r="G5" s="10"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="38"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
       <c r="J5" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K5" s="39" t="s">
+      <c r="K5" s="45" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A6" s="34"/>
-      <c r="B6" s="34"/>
-      <c r="C6" s="34"/>
+      <c r="A6" s="41"/>
+      <c r="B6" s="41"/>
+      <c r="C6" s="41"/>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="41"/>
-      <c r="F6" s="36"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="44"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="38"/>
-      <c r="I6" s="38"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
       <c r="J6" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K6" s="39"/>
+      <c r="K6" s="45"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A7" s="34"/>
-      <c r="B7" s="34"/>
-      <c r="C7" s="34"/>
+      <c r="A7" s="41"/>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
       <c r="D7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="41"/>
-      <c r="F7" s="36"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="44"/>
       <c r="G7" s="10"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="38"/>
+      <c r="H7" s="43"/>
+      <c r="I7" s="43"/>
       <c r="J7" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="K7" s="39"/>
+      <c r="K7" s="45"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A8" s="34"/>
-      <c r="B8" s="34"/>
-      <c r="C8" s="34"/>
+      <c r="A8" s="41"/>
+      <c r="B8" s="41"/>
+      <c r="C8" s="41"/>
       <c r="D8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="41"/>
-      <c r="F8" s="36"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="44"/>
       <c r="G8" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="H8" s="38"/>
-      <c r="I8" s="38"/>
+      <c r="H8" s="43"/>
+      <c r="I8" s="43"/>
       <c r="J8" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="K8" s="39"/>
+      <c r="K8" s="45"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A9" s="34"/>
-      <c r="B9" s="34"/>
-      <c r="C9" s="34"/>
+      <c r="A9" s="41"/>
+      <c r="B9" s="41"/>
+      <c r="C9" s="41"/>
       <c r="D9" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="41"/>
-      <c r="F9" s="36"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="44"/>
       <c r="G9" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="H9" s="38"/>
-      <c r="I9" s="38"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
       <c r="J9" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="K9" s="39"/>
+      <c r="K9" s="45"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A10" s="34"/>
-      <c r="B10" s="34"/>
-      <c r="C10" s="34"/>
+      <c r="A10" s="41"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
       <c r="D10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="41"/>
-      <c r="F10" s="36"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="44"/>
       <c r="G10" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="H10" s="38"/>
-      <c r="I10" s="38"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
       <c r="J10" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="K10" s="39"/>
+      <c r="K10" s="45"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A11" s="34"/>
-      <c r="B11" s="34"/>
-      <c r="C11" s="34"/>
+      <c r="A11" s="41"/>
+      <c r="B11" s="41"/>
+      <c r="C11" s="41"/>
       <c r="D11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="41"/>
-      <c r="F11" s="36"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="44"/>
       <c r="G11" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="H11" s="38"/>
-      <c r="I11" s="38"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="43"/>
       <c r="J11" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="K11" s="39"/>
+      <c r="K11" s="45"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A12" s="34"/>
-      <c r="B12" s="34"/>
-      <c r="C12" s="34"/>
+      <c r="A12" s="41"/>
+      <c r="B12" s="41"/>
+      <c r="C12" s="41"/>
       <c r="D12" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E12" s="41"/>
-      <c r="F12" s="36"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="44"/>
       <c r="G12" s="10"/>
-      <c r="H12" s="38"/>
-      <c r="I12" s="38"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
       <c r="J12" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K12" s="39"/>
+      <c r="K12" s="45"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A13" s="34"/>
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
+      <c r="A13" s="41"/>
+      <c r="B13" s="41"/>
+      <c r="C13" s="41"/>
       <c r="D13" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="41"/>
-      <c r="F13" s="36"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="44"/>
       <c r="G13" s="10"/>
-      <c r="H13" s="38"/>
-      <c r="I13" s="38"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
       <c r="J13" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="K13" s="39"/>
+      <c r="K13" s="45"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A14" s="34"/>
-      <c r="B14" s="34"/>
-      <c r="C14" s="34"/>
+      <c r="A14" s="41"/>
+      <c r="B14" s="41"/>
+      <c r="C14" s="41"/>
       <c r="D14" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="41"/>
-      <c r="F14" s="36"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="44"/>
       <c r="G14" s="10"/>
-      <c r="H14" s="38"/>
-      <c r="I14" s="38"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
       <c r="J14" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="K14" s="39"/>
+      <c r="K14" s="45"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" s="34"/>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
+      <c r="A15" s="41"/>
+      <c r="B15" s="41"/>
+      <c r="C15" s="41"/>
       <c r="D15" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="41"/>
-      <c r="F15" s="36"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="44"/>
       <c r="G15" s="10"/>
-      <c r="H15" s="38"/>
-      <c r="I15" s="38"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
       <c r="J15" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="K15" s="39"/>
+      <c r="K15" s="45"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" s="45"/>
-      <c r="B16" s="45"/>
-      <c r="C16" s="45"/>
+      <c r="A16" s="51"/>
+      <c r="B16" s="51"/>
+      <c r="C16" s="51"/>
       <c r="D16" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="48"/>
-      <c r="F16" s="36"/>
+      <c r="E16" s="50"/>
+      <c r="F16" s="44"/>
       <c r="G16" s="10"/>
       <c r="H16" s="47"/>
       <c r="I16" s="47"/>
       <c r="J16" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="K16" s="39"/>
+      <c r="K16" s="45"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="7"/>
@@ -2401,19 +2440,19 @@
       <c r="J17" s="1"/>
     </row>
     <row r="18" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="33" t="s">
+      <c r="A18" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="B18" s="33" t="s">
+      <c r="B18" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="33" t="s">
+      <c r="C18" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="D18" s="33" t="s">
+      <c r="D18" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="E18" s="40" t="s">
+      <c r="E18" s="48" t="s">
         <v>178</v>
       </c>
       <c r="F18" s="18">
@@ -2422,19 +2461,19 @@
       <c r="G18" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="H18" s="37" t="s">
+      <c r="H18" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="I18" s="37" t="s">
+      <c r="I18" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="J18" s="37" t="s">
+      <c r="J18" s="42" t="s">
         <v>26</v>
       </c>
       <c r="K18" s="46" t="s">
         <v>182</v>
       </c>
-      <c r="L18" s="35"/>
+      <c r="L18" s="37"/>
       <c r="M18" s="1" t="s">
         <v>147</v>
       </c>
@@ -2446,23 +2485,23 @@
       </c>
     </row>
     <row r="19" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="34"/>
-      <c r="B19" s="34"/>
-      <c r="C19" s="34"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="41"/>
+      <c r="A19" s="41"/>
+      <c r="B19" s="41"/>
+      <c r="C19" s="41"/>
+      <c r="D19" s="41"/>
+      <c r="E19" s="49"/>
       <c r="F19" s="19">
         <v>2</v>
       </c>
       <c r="G19" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="H19" s="38"/>
-      <c r="I19" s="38"/>
-      <c r="J19" s="38"/>
-      <c r="K19" s="39"/>
-      <c r="L19" s="36"/>
-      <c r="M19" s="35" t="s">
+      <c r="H19" s="43"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="45"/>
+      <c r="L19" s="44"/>
+      <c r="M19" s="37" t="s">
         <v>150</v>
       </c>
       <c r="N19" s="1">
@@ -2473,23 +2512,23 @@
       </c>
     </row>
     <row r="20" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="34"/>
-      <c r="B20" s="34"/>
-      <c r="C20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="41"/>
+      <c r="A20" s="41"/>
+      <c r="B20" s="41"/>
+      <c r="C20" s="41"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="49"/>
       <c r="F20" s="19">
         <v>14</v>
       </c>
       <c r="G20" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="H20" s="38"/>
-      <c r="I20" s="38"/>
-      <c r="J20" s="38"/>
-      <c r="K20" s="39"/>
-      <c r="L20" s="36"/>
-      <c r="M20" s="36"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="45"/>
+      <c r="L20" s="44"/>
+      <c r="M20" s="44"/>
       <c r="N20" s="1">
         <v>1</v>
       </c>
@@ -2498,23 +2537,23 @@
       </c>
     </row>
     <row r="21" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="34"/>
-      <c r="B21" s="34"/>
-      <c r="C21" s="34"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="41"/>
+      <c r="A21" s="41"/>
+      <c r="B21" s="41"/>
+      <c r="C21" s="41"/>
+      <c r="D21" s="41"/>
+      <c r="E21" s="49"/>
       <c r="F21" s="19">
         <v>6</v>
       </c>
       <c r="G21" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="H21" s="38"/>
-      <c r="I21" s="38"/>
-      <c r="J21" s="38"/>
-      <c r="K21" s="39"/>
-      <c r="L21" s="36"/>
-      <c r="M21" s="36"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="43"/>
+      <c r="K21" s="45"/>
+      <c r="L21" s="44"/>
+      <c r="M21" s="44"/>
       <c r="N21" s="1">
         <v>2</v>
       </c>
@@ -2523,23 +2562,23 @@
       </c>
     </row>
     <row r="22" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="34"/>
-      <c r="B22" s="34"/>
-      <c r="C22" s="34"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="41"/>
+      <c r="A22" s="41"/>
+      <c r="B22" s="41"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="41"/>
+      <c r="E22" s="49"/>
       <c r="F22" s="19">
         <v>6</v>
       </c>
       <c r="G22" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="H22" s="38"/>
-      <c r="I22" s="38"/>
-      <c r="J22" s="38"/>
-      <c r="K22" s="39"/>
-      <c r="L22" s="36"/>
-      <c r="M22" s="36"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="45"/>
+      <c r="L22" s="44"/>
+      <c r="M22" s="44"/>
       <c r="N22" s="1">
         <v>3</v>
       </c>
@@ -2548,23 +2587,23 @@
       </c>
     </row>
     <row r="23" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="34"/>
-      <c r="B23" s="34"/>
-      <c r="C23" s="34"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="41"/>
+      <c r="A23" s="41"/>
+      <c r="B23" s="41"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="41"/>
+      <c r="E23" s="49"/>
       <c r="F23" s="19">
         <v>6</v>
       </c>
       <c r="G23" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="H23" s="38"/>
-      <c r="I23" s="38"/>
-      <c r="J23" s="38"/>
-      <c r="K23" s="39"/>
-      <c r="L23" s="36"/>
-      <c r="M23" s="36"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="43"/>
+      <c r="K23" s="45"/>
+      <c r="L23" s="44"/>
+      <c r="M23" s="44"/>
       <c r="N23" s="1">
         <v>4</v>
       </c>
@@ -2573,23 +2612,23 @@
       </c>
     </row>
     <row r="24" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="34"/>
-      <c r="B24" s="34"/>
-      <c r="C24" s="34"/>
-      <c r="D24" s="34"/>
-      <c r="E24" s="41"/>
+      <c r="A24" s="41"/>
+      <c r="B24" s="41"/>
+      <c r="C24" s="41"/>
+      <c r="D24" s="41"/>
+      <c r="E24" s="49"/>
       <c r="F24" s="19">
         <v>6</v>
       </c>
       <c r="G24" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="H24" s="38"/>
-      <c r="I24" s="38"/>
-      <c r="J24" s="38"/>
-      <c r="K24" s="39"/>
-      <c r="L24" s="36"/>
-      <c r="M24" s="36"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="43"/>
+      <c r="K24" s="45"/>
+      <c r="L24" s="44"/>
+      <c r="M24" s="44"/>
       <c r="N24" s="1">
         <v>5</v>
       </c>
@@ -2598,23 +2637,23 @@
       </c>
     </row>
     <row r="25" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="34"/>
-      <c r="B25" s="34"/>
-      <c r="C25" s="34"/>
-      <c r="D25" s="34"/>
-      <c r="E25" s="41"/>
+      <c r="A25" s="41"/>
+      <c r="B25" s="41"/>
+      <c r="C25" s="41"/>
+      <c r="D25" s="41"/>
+      <c r="E25" s="49"/>
       <c r="F25" s="19">
         <v>6</v>
       </c>
       <c r="G25" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="H25" s="38"/>
-      <c r="I25" s="38"/>
-      <c r="J25" s="38"/>
-      <c r="K25" s="39"/>
-      <c r="L25" s="36"/>
-      <c r="M25" s="36"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="43"/>
+      <c r="K25" s="45"/>
+      <c r="L25" s="44"/>
+      <c r="M25" s="44"/>
       <c r="N25" s="1">
         <v>6</v>
       </c>
@@ -2623,23 +2662,23 @@
       </c>
     </row>
     <row r="26" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="34"/>
-      <c r="B26" s="34"/>
-      <c r="C26" s="34"/>
-      <c r="D26" s="34"/>
-      <c r="E26" s="41"/>
+      <c r="A26" s="41"/>
+      <c r="B26" s="41"/>
+      <c r="C26" s="41"/>
+      <c r="D26" s="41"/>
+      <c r="E26" s="49"/>
       <c r="F26" s="19">
         <v>6</v>
       </c>
       <c r="G26" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="H26" s="38"/>
-      <c r="I26" s="38"/>
-      <c r="J26" s="38"/>
-      <c r="K26" s="39"/>
-      <c r="L26" s="36"/>
-      <c r="M26" s="36"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="43"/>
+      <c r="J26" s="43"/>
+      <c r="K26" s="45"/>
+      <c r="L26" s="44"/>
+      <c r="M26" s="44"/>
       <c r="N26" s="1">
         <v>7</v>
       </c>
@@ -2648,23 +2687,23 @@
       </c>
     </row>
     <row r="27" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="34"/>
-      <c r="B27" s="34"/>
-      <c r="C27" s="34"/>
-      <c r="D27" s="34"/>
-      <c r="E27" s="41"/>
+      <c r="A27" s="41"/>
+      <c r="B27" s="41"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="41"/>
+      <c r="E27" s="49"/>
       <c r="F27" s="19">
         <v>6</v>
       </c>
       <c r="G27" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="H27" s="38"/>
-      <c r="I27" s="38"/>
-      <c r="J27" s="38"/>
-      <c r="K27" s="39"/>
-      <c r="L27" s="36"/>
-      <c r="M27" s="36"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="43"/>
+      <c r="J27" s="43"/>
+      <c r="K27" s="45"/>
+      <c r="L27" s="44"/>
+      <c r="M27" s="44"/>
       <c r="N27" s="1">
         <v>8</v>
       </c>
@@ -2673,23 +2712,23 @@
       </c>
     </row>
     <row r="28" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="34"/>
-      <c r="B28" s="34"/>
-      <c r="C28" s="34"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="41"/>
+      <c r="A28" s="41"/>
+      <c r="B28" s="41"/>
+      <c r="C28" s="41"/>
+      <c r="D28" s="41"/>
+      <c r="E28" s="49"/>
       <c r="F28" s="19">
         <v>6</v>
       </c>
       <c r="G28" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="H28" s="38"/>
-      <c r="I28" s="38"/>
-      <c r="J28" s="38"/>
-      <c r="K28" s="39"/>
-      <c r="L28" s="36"/>
-      <c r="M28" s="36"/>
+      <c r="H28" s="43"/>
+      <c r="I28" s="43"/>
+      <c r="J28" s="43"/>
+      <c r="K28" s="45"/>
+      <c r="L28" s="44"/>
+      <c r="M28" s="44"/>
       <c r="N28" s="1">
         <v>9</v>
       </c>
@@ -2698,23 +2737,23 @@
       </c>
     </row>
     <row r="29" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="34"/>
-      <c r="B29" s="34"/>
-      <c r="C29" s="34"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="41"/>
+      <c r="A29" s="41"/>
+      <c r="B29" s="41"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="49"/>
       <c r="F29" s="19">
         <v>6</v>
       </c>
       <c r="G29" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="H29" s="38"/>
-      <c r="I29" s="38"/>
-      <c r="J29" s="38"/>
-      <c r="K29" s="39"/>
-      <c r="L29" s="36"/>
-      <c r="M29" s="36"/>
+      <c r="H29" s="43"/>
+      <c r="I29" s="43"/>
+      <c r="J29" s="43"/>
+      <c r="K29" s="45"/>
+      <c r="L29" s="44"/>
+      <c r="M29" s="44"/>
       <c r="N29" s="1">
         <v>10</v>
       </c>
@@ -2723,23 +2762,23 @@
       </c>
     </row>
     <row r="30" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="34"/>
-      <c r="B30" s="34"/>
-      <c r="C30" s="34"/>
-      <c r="D30" s="34"/>
-      <c r="E30" s="41"/>
+      <c r="A30" s="41"/>
+      <c r="B30" s="41"/>
+      <c r="C30" s="41"/>
+      <c r="D30" s="41"/>
+      <c r="E30" s="49"/>
       <c r="F30" s="19">
         <v>6</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="H30" s="38"/>
-      <c r="I30" s="38"/>
-      <c r="J30" s="38"/>
-      <c r="K30" s="39"/>
-      <c r="L30" s="36"/>
-      <c r="M30" s="36"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="45"/>
+      <c r="L30" s="44"/>
+      <c r="M30" s="44"/>
       <c r="N30" s="1">
         <v>11</v>
       </c>
@@ -2748,23 +2787,23 @@
       </c>
     </row>
     <row r="31" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="34"/>
-      <c r="B31" s="34"/>
-      <c r="C31" s="34"/>
-      <c r="D31" s="34"/>
-      <c r="E31" s="41"/>
+      <c r="A31" s="41"/>
+      <c r="B31" s="41"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="49"/>
       <c r="F31" s="19">
         <v>6</v>
       </c>
       <c r="G31" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="H31" s="38"/>
-      <c r="I31" s="38"/>
-      <c r="J31" s="38"/>
-      <c r="K31" s="39"/>
-      <c r="L31" s="36"/>
-      <c r="M31" s="43"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="43"/>
+      <c r="J31" s="43"/>
+      <c r="K31" s="45"/>
+      <c r="L31" s="44"/>
+      <c r="M31" s="38"/>
       <c r="N31" s="1" t="s">
         <v>180</v>
       </c>
@@ -2773,23 +2812,23 @@
       </c>
     </row>
     <row r="32" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="34"/>
-      <c r="B32" s="34"/>
-      <c r="C32" s="34"/>
-      <c r="D32" s="34"/>
-      <c r="E32" s="41"/>
+      <c r="A32" s="41"/>
+      <c r="B32" s="41"/>
+      <c r="C32" s="41"/>
+      <c r="D32" s="41"/>
+      <c r="E32" s="49"/>
       <c r="F32" s="19">
         <v>6</v>
       </c>
       <c r="G32" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="H32" s="38"/>
-      <c r="I32" s="38"/>
-      <c r="J32" s="38"/>
-      <c r="K32" s="39"/>
-      <c r="L32" s="36"/>
-      <c r="M32" s="35" t="s">
+      <c r="H32" s="43"/>
+      <c r="I32" s="43"/>
+      <c r="J32" s="43"/>
+      <c r="K32" s="45"/>
+      <c r="L32" s="44"/>
+      <c r="M32" s="37" t="s">
         <v>162</v>
       </c>
       <c r="N32" s="1">
@@ -2800,23 +2839,23 @@
       </c>
     </row>
     <row r="33" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="34"/>
-      <c r="B33" s="34"/>
-      <c r="C33" s="34"/>
-      <c r="D33" s="34"/>
-      <c r="E33" s="41"/>
+      <c r="A33" s="41"/>
+      <c r="B33" s="41"/>
+      <c r="C33" s="41"/>
+      <c r="D33" s="41"/>
+      <c r="E33" s="49"/>
       <c r="F33" s="19">
         <v>6</v>
       </c>
       <c r="G33" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="H33" s="38"/>
-      <c r="I33" s="38"/>
-      <c r="J33" s="38"/>
-      <c r="K33" s="39"/>
-      <c r="L33" s="36"/>
-      <c r="M33" s="36"/>
+      <c r="H33" s="43"/>
+      <c r="I33" s="43"/>
+      <c r="J33" s="43"/>
+      <c r="K33" s="45"/>
+      <c r="L33" s="44"/>
+      <c r="M33" s="44"/>
       <c r="N33" s="1">
         <v>1</v>
       </c>
@@ -2825,23 +2864,23 @@
       </c>
     </row>
     <row r="34" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="34"/>
-      <c r="B34" s="34"/>
-      <c r="C34" s="34"/>
-      <c r="D34" s="34"/>
-      <c r="E34" s="41"/>
+      <c r="A34" s="41"/>
+      <c r="B34" s="41"/>
+      <c r="C34" s="41"/>
+      <c r="D34" s="41"/>
+      <c r="E34" s="49"/>
       <c r="F34" s="19">
         <v>6</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="H34" s="38"/>
-      <c r="I34" s="38"/>
-      <c r="J34" s="38"/>
-      <c r="K34" s="39"/>
-      <c r="L34" s="36"/>
-      <c r="M34" s="36"/>
+      <c r="H34" s="43"/>
+      <c r="I34" s="43"/>
+      <c r="J34" s="43"/>
+      <c r="K34" s="45"/>
+      <c r="L34" s="44"/>
+      <c r="M34" s="44"/>
       <c r="N34" s="1">
         <v>2</v>
       </c>
@@ -2850,23 +2889,23 @@
       </c>
     </row>
     <row r="35" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="34"/>
-      <c r="B35" s="34"/>
-      <c r="C35" s="34"/>
-      <c r="D35" s="34"/>
-      <c r="E35" s="41"/>
+      <c r="A35" s="41"/>
+      <c r="B35" s="41"/>
+      <c r="C35" s="41"/>
+      <c r="D35" s="41"/>
+      <c r="E35" s="49"/>
       <c r="F35" s="19">
         <v>6</v>
       </c>
       <c r="G35" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="H35" s="38"/>
-      <c r="I35" s="38"/>
-      <c r="J35" s="38"/>
-      <c r="K35" s="39"/>
-      <c r="L35" s="36"/>
-      <c r="M35" s="36"/>
+      <c r="H35" s="43"/>
+      <c r="I35" s="43"/>
+      <c r="J35" s="43"/>
+      <c r="K35" s="45"/>
+      <c r="L35" s="44"/>
+      <c r="M35" s="44"/>
       <c r="N35" s="1">
         <v>3</v>
       </c>
@@ -2875,23 +2914,23 @@
       </c>
     </row>
     <row r="36" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="34"/>
-      <c r="B36" s="34"/>
-      <c r="C36" s="34"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="41"/>
+      <c r="A36" s="41"/>
+      <c r="B36" s="41"/>
+      <c r="C36" s="41"/>
+      <c r="D36" s="41"/>
+      <c r="E36" s="49"/>
       <c r="F36" s="19">
         <v>6</v>
       </c>
       <c r="G36" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="H36" s="38"/>
-      <c r="I36" s="38"/>
-      <c r="J36" s="38"/>
-      <c r="K36" s="39"/>
-      <c r="L36" s="36"/>
-      <c r="M36" s="43"/>
+      <c r="H36" s="43"/>
+      <c r="I36" s="43"/>
+      <c r="J36" s="43"/>
+      <c r="K36" s="45"/>
+      <c r="L36" s="44"/>
+      <c r="M36" s="38"/>
       <c r="N36" s="1" t="s">
         <v>167</v>
       </c>
@@ -2900,23 +2939,23 @@
       </c>
     </row>
     <row r="37" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="34"/>
-      <c r="B37" s="34"/>
-      <c r="C37" s="34"/>
-      <c r="D37" s="34"/>
-      <c r="E37" s="41"/>
+      <c r="A37" s="41"/>
+      <c r="B37" s="41"/>
+      <c r="C37" s="41"/>
+      <c r="D37" s="41"/>
+      <c r="E37" s="49"/>
       <c r="F37" s="19">
         <v>6</v>
       </c>
       <c r="G37" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="H37" s="38"/>
-      <c r="I37" s="38"/>
-      <c r="J37" s="38"/>
-      <c r="K37" s="39"/>
-      <c r="L37" s="36"/>
-      <c r="M37" s="35" t="s">
+      <c r="H37" s="43"/>
+      <c r="I37" s="43"/>
+      <c r="J37" s="43"/>
+      <c r="K37" s="45"/>
+      <c r="L37" s="44"/>
+      <c r="M37" s="37" t="s">
         <v>168</v>
       </c>
       <c r="N37" s="1">
@@ -2927,23 +2966,23 @@
       </c>
     </row>
     <row r="38" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="34"/>
-      <c r="B38" s="34"/>
-      <c r="C38" s="34"/>
-      <c r="D38" s="34"/>
-      <c r="E38" s="41"/>
+      <c r="A38" s="41"/>
+      <c r="B38" s="41"/>
+      <c r="C38" s="41"/>
+      <c r="D38" s="41"/>
+      <c r="E38" s="49"/>
       <c r="F38" s="19">
         <v>6</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="H38" s="38"/>
-      <c r="I38" s="38"/>
-      <c r="J38" s="38"/>
-      <c r="K38" s="39"/>
-      <c r="L38" s="36"/>
-      <c r="M38" s="36"/>
+      <c r="H38" s="43"/>
+      <c r="I38" s="43"/>
+      <c r="J38" s="43"/>
+      <c r="K38" s="45"/>
+      <c r="L38" s="44"/>
+      <c r="M38" s="44"/>
       <c r="N38" s="1">
         <v>1</v>
       </c>
@@ -2952,23 +2991,23 @@
       </c>
     </row>
     <row r="39" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="34"/>
-      <c r="B39" s="34"/>
-      <c r="C39" s="34"/>
-      <c r="D39" s="34"/>
-      <c r="E39" s="41"/>
+      <c r="A39" s="41"/>
+      <c r="B39" s="41"/>
+      <c r="C39" s="41"/>
+      <c r="D39" s="41"/>
+      <c r="E39" s="49"/>
       <c r="F39" s="19">
         <v>6</v>
       </c>
       <c r="G39" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="H39" s="38"/>
-      <c r="I39" s="38"/>
-      <c r="J39" s="38"/>
-      <c r="K39" s="39"/>
-      <c r="L39" s="36"/>
-      <c r="M39" s="36"/>
+      <c r="H39" s="43"/>
+      <c r="I39" s="43"/>
+      <c r="J39" s="43"/>
+      <c r="K39" s="45"/>
+      <c r="L39" s="44"/>
+      <c r="M39" s="44"/>
       <c r="N39" s="1">
         <v>2</v>
       </c>
@@ -2977,23 +3016,23 @@
       </c>
     </row>
     <row r="40" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="34"/>
-      <c r="B40" s="34"/>
-      <c r="C40" s="34"/>
-      <c r="D40" s="34"/>
-      <c r="E40" s="41"/>
+      <c r="A40" s="41"/>
+      <c r="B40" s="41"/>
+      <c r="C40" s="41"/>
+      <c r="D40" s="41"/>
+      <c r="E40" s="49"/>
       <c r="F40" s="19">
         <v>6</v>
       </c>
       <c r="G40" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="H40" s="38"/>
-      <c r="I40" s="38"/>
-      <c r="J40" s="38"/>
-      <c r="K40" s="39"/>
-      <c r="L40" s="36"/>
-      <c r="M40" s="36"/>
+      <c r="H40" s="43"/>
+      <c r="I40" s="43"/>
+      <c r="J40" s="43"/>
+      <c r="K40" s="45"/>
+      <c r="L40" s="44"/>
+      <c r="M40" s="44"/>
       <c r="N40" s="1">
         <v>3</v>
       </c>
@@ -3002,23 +3041,23 @@
       </c>
     </row>
     <row r="41" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="34"/>
-      <c r="B41" s="34"/>
-      <c r="C41" s="34"/>
-      <c r="D41" s="34"/>
-      <c r="E41" s="41"/>
+      <c r="A41" s="41"/>
+      <c r="B41" s="41"/>
+      <c r="C41" s="41"/>
+      <c r="D41" s="41"/>
+      <c r="E41" s="49"/>
       <c r="F41" s="19">
         <v>6</v>
       </c>
       <c r="G41" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="H41" s="38"/>
-      <c r="I41" s="38"/>
-      <c r="J41" s="38"/>
-      <c r="K41" s="39"/>
-      <c r="L41" s="36"/>
-      <c r="M41" s="36"/>
+      <c r="H41" s="43"/>
+      <c r="I41" s="43"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="45"/>
+      <c r="L41" s="44"/>
+      <c r="M41" s="44"/>
       <c r="N41" s="1">
         <v>4</v>
       </c>
@@ -3027,23 +3066,23 @@
       </c>
     </row>
     <row r="42" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="34"/>
-      <c r="B42" s="34"/>
-      <c r="C42" s="34"/>
-      <c r="D42" s="34"/>
-      <c r="E42" s="41"/>
+      <c r="A42" s="41"/>
+      <c r="B42" s="41"/>
+      <c r="C42" s="41"/>
+      <c r="D42" s="41"/>
+      <c r="E42" s="49"/>
       <c r="F42" s="19">
         <v>6</v>
       </c>
       <c r="G42" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="H42" s="38"/>
-      <c r="I42" s="38"/>
-      <c r="J42" s="38"/>
-      <c r="K42" s="39"/>
-      <c r="L42" s="36"/>
-      <c r="M42" s="36"/>
+      <c r="H42" s="43"/>
+      <c r="I42" s="43"/>
+      <c r="J42" s="43"/>
+      <c r="K42" s="45"/>
+      <c r="L42" s="44"/>
+      <c r="M42" s="44"/>
       <c r="N42" s="1">
         <v>5</v>
       </c>
@@ -3052,23 +3091,23 @@
       </c>
     </row>
     <row r="43" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="34"/>
-      <c r="B43" s="34"/>
-      <c r="C43" s="34"/>
-      <c r="D43" s="34"/>
-      <c r="E43" s="41"/>
+      <c r="A43" s="41"/>
+      <c r="B43" s="41"/>
+      <c r="C43" s="41"/>
+      <c r="D43" s="41"/>
+      <c r="E43" s="49"/>
       <c r="F43" s="19">
         <v>6</v>
       </c>
       <c r="G43" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="H43" s="38"/>
-      <c r="I43" s="38"/>
-      <c r="J43" s="38"/>
-      <c r="K43" s="39"/>
-      <c r="L43" s="36"/>
-      <c r="M43" s="43"/>
+      <c r="H43" s="43"/>
+      <c r="I43" s="43"/>
+      <c r="J43" s="43"/>
+      <c r="K43" s="45"/>
+      <c r="L43" s="44"/>
+      <c r="M43" s="38"/>
       <c r="N43" s="1" t="s">
         <v>175</v>
       </c>
@@ -3077,22 +3116,22 @@
       </c>
     </row>
     <row r="44" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="34"/>
-      <c r="B44" s="34"/>
-      <c r="C44" s="34"/>
-      <c r="D44" s="34"/>
-      <c r="E44" s="41"/>
+      <c r="A44" s="41"/>
+      <c r="B44" s="41"/>
+      <c r="C44" s="41"/>
+      <c r="D44" s="41"/>
+      <c r="E44" s="49"/>
       <c r="F44" s="19">
         <v>8</v>
       </c>
       <c r="G44" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="H44" s="38"/>
-      <c r="I44" s="38"/>
-      <c r="J44" s="38"/>
-      <c r="K44" s="39"/>
-      <c r="L44" s="36"/>
+      <c r="H44" s="43"/>
+      <c r="I44" s="43"/>
+      <c r="J44" s="43"/>
+      <c r="K44" s="45"/>
+      <c r="L44" s="44"/>
       <c r="M44" s="1" t="s">
         <v>176</v>
       </c>
@@ -3102,119 +3141,119 @@
       <c r="O44" s="1"/>
     </row>
     <row r="45" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="34"/>
-      <c r="B45" s="34"/>
-      <c r="C45" s="34"/>
-      <c r="D45" s="34"/>
-      <c r="E45" s="41"/>
+      <c r="A45" s="41"/>
+      <c r="B45" s="41"/>
+      <c r="C45" s="41"/>
+      <c r="D45" s="41"/>
+      <c r="E45" s="49"/>
       <c r="F45" s="19">
         <v>8</v>
       </c>
       <c r="G45" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="H45" s="38"/>
-      <c r="I45" s="38"/>
-      <c r="J45" s="38"/>
-      <c r="K45" s="39"/>
-      <c r="L45" s="36"/>
+      <c r="H45" s="43"/>
+      <c r="I45" s="43"/>
+      <c r="J45" s="43"/>
+      <c r="K45" s="45"/>
+      <c r="L45" s="44"/>
     </row>
     <row r="46" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="34"/>
-      <c r="B46" s="34"/>
-      <c r="C46" s="34"/>
-      <c r="D46" s="34"/>
-      <c r="E46" s="41"/>
+      <c r="A46" s="41"/>
+      <c r="B46" s="41"/>
+      <c r="C46" s="41"/>
+      <c r="D46" s="41"/>
+      <c r="E46" s="49"/>
       <c r="F46" s="19">
         <v>6</v>
       </c>
       <c r="G46" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="H46" s="38"/>
-      <c r="I46" s="38"/>
-      <c r="J46" s="38"/>
-      <c r="K46" s="39"/>
-      <c r="L46" s="36"/>
+      <c r="H46" s="43"/>
+      <c r="I46" s="43"/>
+      <c r="J46" s="43"/>
+      <c r="K46" s="45"/>
+      <c r="L46" s="44"/>
     </row>
     <row r="47" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="34"/>
-      <c r="B47" s="34"/>
-      <c r="C47" s="34"/>
-      <c r="D47" s="34"/>
-      <c r="E47" s="41"/>
+      <c r="A47" s="41"/>
+      <c r="B47" s="41"/>
+      <c r="C47" s="41"/>
+      <c r="D47" s="41"/>
+      <c r="E47" s="49"/>
       <c r="F47" s="19">
         <v>6</v>
       </c>
       <c r="G47" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="H47" s="38"/>
-      <c r="I47" s="38"/>
-      <c r="J47" s="38"/>
-      <c r="K47" s="39"/>
-      <c r="L47" s="36"/>
+      <c r="H47" s="43"/>
+      <c r="I47" s="43"/>
+      <c r="J47" s="43"/>
+      <c r="K47" s="45"/>
+      <c r="L47" s="44"/>
     </row>
     <row r="48" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="34"/>
-      <c r="B48" s="34"/>
-      <c r="C48" s="34"/>
-      <c r="D48" s="34"/>
-      <c r="E48" s="41"/>
+      <c r="A48" s="41"/>
+      <c r="B48" s="41"/>
+      <c r="C48" s="41"/>
+      <c r="D48" s="41"/>
+      <c r="E48" s="49"/>
       <c r="F48" s="19">
         <v>6</v>
       </c>
       <c r="G48" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="H48" s="38"/>
-      <c r="I48" s="38"/>
-      <c r="J48" s="38"/>
-      <c r="K48" s="39"/>
-      <c r="L48" s="36"/>
+      <c r="H48" s="43"/>
+      <c r="I48" s="43"/>
+      <c r="J48" s="43"/>
+      <c r="K48" s="45"/>
+      <c r="L48" s="44"/>
     </row>
     <row r="49" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="34"/>
-      <c r="B49" s="34"/>
-      <c r="C49" s="34"/>
-      <c r="D49" s="34"/>
-      <c r="E49" s="41"/>
+      <c r="A49" s="41"/>
+      <c r="B49" s="41"/>
+      <c r="C49" s="41"/>
+      <c r="D49" s="41"/>
+      <c r="E49" s="49"/>
       <c r="F49" s="19">
         <v>6</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="H49" s="38"/>
-      <c r="I49" s="38"/>
-      <c r="J49" s="38"/>
-      <c r="K49" s="39"/>
-      <c r="L49" s="36"/>
+      <c r="H49" s="43"/>
+      <c r="I49" s="43"/>
+      <c r="J49" s="43"/>
+      <c r="K49" s="45"/>
+      <c r="L49" s="44"/>
     </row>
     <row r="50" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="34"/>
-      <c r="B50" s="34"/>
-      <c r="C50" s="34"/>
-      <c r="D50" s="34"/>
-      <c r="E50" s="41"/>
+      <c r="A50" s="41"/>
+      <c r="B50" s="41"/>
+      <c r="C50" s="41"/>
+      <c r="D50" s="41"/>
+      <c r="E50" s="49"/>
       <c r="F50" s="19">
         <v>6</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="H50" s="38"/>
-      <c r="I50" s="38"/>
-      <c r="J50" s="38"/>
-      <c r="K50" s="39"/>
-      <c r="L50" s="36"/>
+      <c r="H50" s="43"/>
+      <c r="I50" s="43"/>
+      <c r="J50" s="43"/>
+      <c r="K50" s="45"/>
+      <c r="L50" s="44"/>
     </row>
     <row r="51" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="16"/>
       <c r="B51" s="16"/>
       <c r="C51" s="16"/>
       <c r="D51" s="16"/>
-      <c r="E51" s="48"/>
+      <c r="E51" s="50"/>
       <c r="F51" s="19">
         <v>6</v>
       </c>
@@ -4270,12 +4309,18 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="D18:D50"/>
-    <mergeCell ref="J18:J50"/>
-    <mergeCell ref="L18:L50"/>
-    <mergeCell ref="M19:M31"/>
-    <mergeCell ref="M32:M36"/>
-    <mergeCell ref="M37:M43"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="A4:A16"/>
+    <mergeCell ref="B4:B16"/>
+    <mergeCell ref="C4:C16"/>
+    <mergeCell ref="C18:C50"/>
+    <mergeCell ref="B18:B50"/>
+    <mergeCell ref="A18:A50"/>
     <mergeCell ref="E52:E87"/>
     <mergeCell ref="K5:K16"/>
     <mergeCell ref="K2:K3"/>
@@ -4287,18 +4332,12 @@
     <mergeCell ref="I4:I16"/>
     <mergeCell ref="E5:E16"/>
     <mergeCell ref="E18:E51"/>
-    <mergeCell ref="A4:A16"/>
-    <mergeCell ref="B4:B16"/>
-    <mergeCell ref="C4:C16"/>
-    <mergeCell ref="C18:C50"/>
-    <mergeCell ref="B18:B50"/>
-    <mergeCell ref="A18:A50"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="D18:D50"/>
+    <mergeCell ref="J18:J50"/>
+    <mergeCell ref="L18:L50"/>
+    <mergeCell ref="M19:M31"/>
+    <mergeCell ref="M32:M36"/>
+    <mergeCell ref="M37:M43"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A4:E4 K60 A18:E18 D5:D17 A2:K2 K52:K56 A3:F3 H3:J3 K17 K4:K5 E52 D52:D84 D86:D88 A52:C88 K62 J4:J18 J52:J88">

--- a/doc/5、开发文档/DFDL33-SH8619 协议转换单元DLT64点表.xlsx
+++ b/doc/5、开发文档/DFDL33-SH8619 协议转换单元DLT64点表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Project\SVN\DFDL33-SH8619\doc\5、开发文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A625E593-6DAD-4DE5-9649-4B393DE2376E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9764043C-622F-4474-8A47-C40767D51AAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="2775" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="220">
   <si>
     <t>00</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -888,6 +888,10 @@
   </si>
   <si>
     <t>电源接入220V，写1进行电压校准</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>80</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1125,6 +1129,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1134,9 +1141,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1161,6 +1165,15 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1170,12 +1183,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1187,9 +1194,6 @@
     </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1550,13 +1554,13 @@
       <c r="K1" s="13"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="30" t="s">
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="31" t="s">
         <v>3</v>
       </c>
       <c r="F2" s="34" t="s">
@@ -1565,14 +1569,14 @@
       <c r="G2" s="37" t="s">
         <v>137</v>
       </c>
-      <c r="H2" s="30" t="s">
+      <c r="H2" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="30"/>
+      <c r="I2" s="31"/>
       <c r="J2" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="31" t="s">
+      <c r="K2" s="32" t="s">
         <v>144</v>
       </c>
     </row>
@@ -1589,7 +1593,7 @@
       <c r="D3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="30"/>
+      <c r="E3" s="31"/>
       <c r="F3" s="34"/>
       <c r="G3" s="38"/>
       <c r="H3" s="1" t="s">
@@ -1599,16 +1603,16 @@
         <v>11</v>
       </c>
       <c r="J3" s="39"/>
-      <c r="K3" s="32"/>
+      <c r="K3" s="33"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="33" t="s">
+      <c r="A4" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="30" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="C4" s="30" t="s">
         <v>184</v>
       </c>
       <c r="D4" s="2" t="s">
@@ -1621,10 +1625,10 @@
         <v>186</v>
       </c>
       <c r="G4" s="21"/>
-      <c r="H4" s="30" t="s">
+      <c r="H4" s="31" t="s">
         <v>39</v>
       </c>
-      <c r="I4" s="30" t="s">
+      <c r="I4" s="31" t="s">
         <v>14</v>
       </c>
       <c r="J4" s="1" t="s">
@@ -1633,17 +1637,17 @@
       <c r="K4" s="29"/>
     </row>
     <row r="5" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="33"/>
-      <c r="B5" s="33"/>
-      <c r="C5" s="33"/>
+      <c r="A5" s="30"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
       <c r="D5" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E5" s="36"/>
       <c r="F5" s="34"/>
       <c r="G5" s="21"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="30"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="31"/>
       <c r="J5" s="1" t="s">
         <v>188</v>
       </c>
@@ -1652,26 +1656,26 @@
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="33"/>
-      <c r="B6" s="33"/>
-      <c r="C6" s="33"/>
+      <c r="A6" s="30"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="30"/>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="36"/>
       <c r="F6" s="34"/>
       <c r="G6" s="21"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="30"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
       <c r="J6" s="1" t="s">
         <v>189</v>
       </c>
       <c r="K6" s="35"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="33"/>
-      <c r="B7" s="33"/>
-      <c r="C7" s="33"/>
+      <c r="A7" s="30"/>
+      <c r="B7" s="30"/>
+      <c r="C7" s="30"/>
       <c r="D7" s="2" t="s">
         <v>16</v>
       </c>
@@ -1680,17 +1684,17 @@
       <c r="G7" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
       <c r="J7" s="1" t="s">
         <v>190</v>
       </c>
       <c r="K7" s="35"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="33"/>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
+      <c r="A8" s="30"/>
+      <c r="B8" s="30"/>
+      <c r="C8" s="30"/>
       <c r="D8" s="2" t="s">
         <v>12</v>
       </c>
@@ -1699,59 +1703,59 @@
       <c r="G8" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="H8" s="30"/>
-      <c r="I8" s="30"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="31"/>
       <c r="J8" s="1" t="s">
         <v>191</v>
       </c>
       <c r="K8" s="35"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="33"/>
-      <c r="B9" s="33"/>
-      <c r="C9" s="33"/>
+      <c r="A9" s="30"/>
+      <c r="B9" s="30"/>
+      <c r="C9" s="30"/>
       <c r="D9" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E9" s="36"/>
       <c r="F9" s="34"/>
       <c r="G9" s="1"/>
-      <c r="H9" s="30"/>
-      <c r="I9" s="30"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
       <c r="J9" s="1" t="s">
         <v>192</v>
       </c>
       <c r="K9" s="35"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="33"/>
-      <c r="B10" s="33"/>
-      <c r="C10" s="33"/>
+      <c r="A10" s="30"/>
+      <c r="B10" s="30"/>
+      <c r="C10" s="30"/>
       <c r="D10" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E10" s="36"/>
       <c r="F10" s="34"/>
       <c r="G10" s="1"/>
-      <c r="H10" s="30"/>
-      <c r="I10" s="30"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="31"/>
       <c r="J10" s="1" t="s">
         <v>193</v>
       </c>
       <c r="K10" s="35"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="33"/>
-      <c r="B11" s="33"/>
-      <c r="C11" s="33"/>
+      <c r="A11" s="30"/>
+      <c r="B11" s="30"/>
+      <c r="C11" s="30"/>
       <c r="D11" s="2" t="s">
         <v>21</v>
       </c>
       <c r="E11" s="36"/>
       <c r="F11" s="34"/>
       <c r="G11" s="1"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="31"/>
       <c r="J11" s="1" t="s">
         <v>194</v>
       </c>
@@ -1915,16 +1919,16 @@
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="33" t="s">
+      <c r="A19" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="33" t="s">
+      <c r="B19" s="30" t="s">
         <v>183</v>
       </c>
-      <c r="C19" s="33" t="s">
+      <c r="C19" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="D19" s="33" t="s">
+      <c r="D19" s="30" t="s">
         <v>203</v>
       </c>
       <c r="E19" s="27" t="s">
@@ -1932,10 +1936,10 @@
       </c>
       <c r="F19" s="27"/>
       <c r="G19" s="27"/>
-      <c r="H19" s="30" t="s">
+      <c r="H19" s="31" t="s">
         <v>215</v>
       </c>
-      <c r="I19" s="30" t="s">
+      <c r="I19" s="31" t="s">
         <v>14</v>
       </c>
       <c r="J19" s="27" t="s">
@@ -1944,34 +1948,34 @@
       <c r="K19" s="28"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="33"/>
-      <c r="B20" s="33"/>
-      <c r="C20" s="33"/>
-      <c r="D20" s="33"/>
+      <c r="A20" s="30"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
       <c r="E20" s="27" t="s">
         <v>204</v>
       </c>
       <c r="F20" s="27"/>
       <c r="G20" s="27"/>
-      <c r="H20" s="30"/>
-      <c r="I20" s="30"/>
+      <c r="H20" s="31"/>
+      <c r="I20" s="31"/>
       <c r="J20" s="27" t="s">
         <v>207</v>
       </c>
       <c r="K20" s="28"/>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="33"/>
-      <c r="B21" s="33"/>
-      <c r="C21" s="33"/>
-      <c r="D21" s="33"/>
+      <c r="A21" s="30"/>
+      <c r="B21" s="30"/>
+      <c r="C21" s="30"/>
+      <c r="D21" s="30"/>
       <c r="E21" s="27" t="s">
         <v>204</v>
       </c>
       <c r="F21" s="27"/>
       <c r="G21" s="27"/>
-      <c r="H21" s="30"/>
-      <c r="I21" s="30"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="31"/>
       <c r="J21" s="27" t="s">
         <v>208</v>
       </c>
@@ -1982,7 +1986,7 @@
         <v>1</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>184</v>
+        <v>219</v>
       </c>
       <c r="C23" s="26" t="s">
         <v>0</v>
@@ -2008,11 +2012,6 @@
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="C19:C21"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="H19:H21"/>
     <mergeCell ref="I19:I21"/>
     <mergeCell ref="K2:K3"/>
     <mergeCell ref="A4:A11"/>
@@ -2029,6 +2028,11 @@
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="J2:J3"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="H19:H21"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A19:D19">
@@ -2131,13 +2135,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30" t="s">
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31" t="s">
         <v>3</v>
       </c>
       <c r="F2" s="34" t="s">
@@ -2146,14 +2150,14 @@
       <c r="G2" s="37" t="s">
         <v>137</v>
       </c>
-      <c r="H2" s="30" t="s">
+      <c r="H2" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="30"/>
+      <c r="I2" s="31"/>
       <c r="J2" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="31" t="s">
+      <c r="K2" s="32" t="s">
         <v>144</v>
       </c>
     </row>
@@ -2170,7 +2174,7 @@
       <c r="D3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="30"/>
+      <c r="E3" s="31"/>
       <c r="F3" s="34"/>
       <c r="G3" s="38"/>
       <c r="H3" s="1" t="s">
@@ -2180,7 +2184,7 @@
         <v>11</v>
       </c>
       <c r="J3" s="39"/>
-      <c r="K3" s="32"/>
+      <c r="K3" s="33"/>
     </row>
     <row r="4" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="40" t="s">
@@ -2202,10 +2206,10 @@
         <v>45</v>
       </c>
       <c r="G4" s="9"/>
-      <c r="H4" s="42" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="42" t="s">
+      <c r="H4" s="45" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="45" t="s">
         <v>14</v>
       </c>
       <c r="J4" s="1" t="s">
@@ -2220,17 +2224,17 @@
       <c r="D5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="48" t="s">
+      <c r="E5" s="49" t="s">
         <v>136</v>
       </c>
-      <c r="F5" s="44"/>
+      <c r="F5" s="47"/>
       <c r="G5" s="10"/>
-      <c r="H5" s="43"/>
-      <c r="I5" s="43"/>
+      <c r="H5" s="46"/>
+      <c r="I5" s="46"/>
       <c r="J5" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K5" s="45" t="s">
+      <c r="K5" s="43" t="s">
         <v>143</v>
       </c>
     </row>
@@ -2241,15 +2245,15 @@
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="49"/>
-      <c r="F6" s="44"/>
+      <c r="E6" s="50"/>
+      <c r="F6" s="47"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="43"/>
-      <c r="I6" s="43"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="46"/>
       <c r="J6" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K6" s="45"/>
+      <c r="K6" s="43"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="41"/>
@@ -2258,15 +2262,15 @@
       <c r="D7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="49"/>
-      <c r="F7" s="44"/>
+      <c r="E7" s="50"/>
+      <c r="F7" s="47"/>
       <c r="G7" s="10"/>
-      <c r="H7" s="43"/>
-      <c r="I7" s="43"/>
+      <c r="H7" s="46"/>
+      <c r="I7" s="46"/>
       <c r="J7" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="K7" s="45"/>
+      <c r="K7" s="43"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="41"/>
@@ -2275,17 +2279,17 @@
       <c r="D8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="49"/>
-      <c r="F8" s="44"/>
+      <c r="E8" s="50"/>
+      <c r="F8" s="47"/>
       <c r="G8" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="H8" s="43"/>
-      <c r="I8" s="43"/>
+      <c r="H8" s="46"/>
+      <c r="I8" s="46"/>
       <c r="J8" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="K8" s="45"/>
+      <c r="K8" s="43"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="41"/>
@@ -2294,17 +2298,17 @@
       <c r="D9" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="49"/>
-      <c r="F9" s="44"/>
+      <c r="E9" s="50"/>
+      <c r="F9" s="47"/>
       <c r="G9" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="H9" s="43"/>
-      <c r="I9" s="43"/>
+      <c r="H9" s="46"/>
+      <c r="I9" s="46"/>
       <c r="J9" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="K9" s="45"/>
+      <c r="K9" s="43"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="41"/>
@@ -2313,17 +2317,17 @@
       <c r="D10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="49"/>
-      <c r="F10" s="44"/>
+      <c r="E10" s="50"/>
+      <c r="F10" s="47"/>
       <c r="G10" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="H10" s="43"/>
-      <c r="I10" s="43"/>
+      <c r="H10" s="46"/>
+      <c r="I10" s="46"/>
       <c r="J10" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="K10" s="45"/>
+      <c r="K10" s="43"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="41"/>
@@ -2332,17 +2336,17 @@
       <c r="D11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="49"/>
-      <c r="F11" s="44"/>
+      <c r="E11" s="50"/>
+      <c r="F11" s="47"/>
       <c r="G11" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="H11" s="43"/>
-      <c r="I11" s="43"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="46"/>
       <c r="J11" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="K11" s="45"/>
+      <c r="K11" s="43"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="41"/>
@@ -2351,15 +2355,15 @@
       <c r="D12" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E12" s="49"/>
-      <c r="F12" s="44"/>
+      <c r="E12" s="50"/>
+      <c r="F12" s="47"/>
       <c r="G12" s="10"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="43"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="46"/>
       <c r="J12" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K12" s="45"/>
+      <c r="K12" s="43"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="41"/>
@@ -2368,15 +2372,15 @@
       <c r="D13" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="49"/>
-      <c r="F13" s="44"/>
+      <c r="E13" s="50"/>
+      <c r="F13" s="47"/>
       <c r="G13" s="10"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="43"/>
+      <c r="H13" s="46"/>
+      <c r="I13" s="46"/>
       <c r="J13" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="K13" s="45"/>
+      <c r="K13" s="43"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="41"/>
@@ -2385,15 +2389,15 @@
       <c r="D14" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="49"/>
-      <c r="F14" s="44"/>
+      <c r="E14" s="50"/>
+      <c r="F14" s="47"/>
       <c r="G14" s="10"/>
-      <c r="H14" s="43"/>
-      <c r="I14" s="43"/>
+      <c r="H14" s="46"/>
+      <c r="I14" s="46"/>
       <c r="J14" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="K14" s="45"/>
+      <c r="K14" s="43"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="41"/>
@@ -2402,32 +2406,32 @@
       <c r="D15" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="49"/>
-      <c r="F15" s="44"/>
+      <c r="E15" s="50"/>
+      <c r="F15" s="47"/>
       <c r="G15" s="10"/>
-      <c r="H15" s="43"/>
-      <c r="I15" s="43"/>
+      <c r="H15" s="46"/>
+      <c r="I15" s="46"/>
       <c r="J15" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="K15" s="45"/>
+      <c r="K15" s="43"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" s="51"/>
-      <c r="B16" s="51"/>
-      <c r="C16" s="51"/>
+      <c r="A16" s="42"/>
+      <c r="B16" s="42"/>
+      <c r="C16" s="42"/>
       <c r="D16" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="50"/>
-      <c r="F16" s="44"/>
+      <c r="E16" s="51"/>
+      <c r="F16" s="47"/>
       <c r="G16" s="10"/>
-      <c r="H16" s="47"/>
-      <c r="I16" s="47"/>
+      <c r="H16" s="48"/>
+      <c r="I16" s="48"/>
       <c r="J16" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="K16" s="45"/>
+      <c r="K16" s="43"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="7"/>
@@ -2452,7 +2456,7 @@
       <c r="D18" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="E18" s="48" t="s">
+      <c r="E18" s="49" t="s">
         <v>178</v>
       </c>
       <c r="F18" s="18">
@@ -2461,16 +2465,16 @@
       <c r="G18" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="H18" s="42" t="s">
+      <c r="H18" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="I18" s="42" t="s">
+      <c r="I18" s="45" t="s">
         <v>39</v>
       </c>
-      <c r="J18" s="42" t="s">
+      <c r="J18" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="K18" s="46" t="s">
+      <c r="K18" s="44" t="s">
         <v>182</v>
       </c>
       <c r="L18" s="37"/>
@@ -2489,18 +2493,18 @@
       <c r="B19" s="41"/>
       <c r="C19" s="41"/>
       <c r="D19" s="41"/>
-      <c r="E19" s="49"/>
+      <c r="E19" s="50"/>
       <c r="F19" s="19">
         <v>2</v>
       </c>
       <c r="G19" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="H19" s="43"/>
-      <c r="I19" s="43"/>
-      <c r="J19" s="43"/>
-      <c r="K19" s="45"/>
-      <c r="L19" s="44"/>
+      <c r="H19" s="46"/>
+      <c r="I19" s="46"/>
+      <c r="J19" s="46"/>
+      <c r="K19" s="43"/>
+      <c r="L19" s="47"/>
       <c r="M19" s="37" t="s">
         <v>150</v>
       </c>
@@ -2516,19 +2520,19 @@
       <c r="B20" s="41"/>
       <c r="C20" s="41"/>
       <c r="D20" s="41"/>
-      <c r="E20" s="49"/>
+      <c r="E20" s="50"/>
       <c r="F20" s="19">
         <v>14</v>
       </c>
       <c r="G20" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="H20" s="43"/>
-      <c r="I20" s="43"/>
-      <c r="J20" s="43"/>
-      <c r="K20" s="45"/>
-      <c r="L20" s="44"/>
-      <c r="M20" s="44"/>
+      <c r="H20" s="46"/>
+      <c r="I20" s="46"/>
+      <c r="J20" s="46"/>
+      <c r="K20" s="43"/>
+      <c r="L20" s="47"/>
+      <c r="M20" s="47"/>
       <c r="N20" s="1">
         <v>1</v>
       </c>
@@ -2541,19 +2545,19 @@
       <c r="B21" s="41"/>
       <c r="C21" s="41"/>
       <c r="D21" s="41"/>
-      <c r="E21" s="49"/>
+      <c r="E21" s="50"/>
       <c r="F21" s="19">
         <v>6</v>
       </c>
       <c r="G21" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="H21" s="43"/>
-      <c r="I21" s="43"/>
-      <c r="J21" s="43"/>
-      <c r="K21" s="45"/>
-      <c r="L21" s="44"/>
-      <c r="M21" s="44"/>
+      <c r="H21" s="46"/>
+      <c r="I21" s="46"/>
+      <c r="J21" s="46"/>
+      <c r="K21" s="43"/>
+      <c r="L21" s="47"/>
+      <c r="M21" s="47"/>
       <c r="N21" s="1">
         <v>2</v>
       </c>
@@ -2566,19 +2570,19 @@
       <c r="B22" s="41"/>
       <c r="C22" s="41"/>
       <c r="D22" s="41"/>
-      <c r="E22" s="49"/>
+      <c r="E22" s="50"/>
       <c r="F22" s="19">
         <v>6</v>
       </c>
       <c r="G22" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="H22" s="43"/>
-      <c r="I22" s="43"/>
-      <c r="J22" s="43"/>
-      <c r="K22" s="45"/>
-      <c r="L22" s="44"/>
-      <c r="M22" s="44"/>
+      <c r="H22" s="46"/>
+      <c r="I22" s="46"/>
+      <c r="J22" s="46"/>
+      <c r="K22" s="43"/>
+      <c r="L22" s="47"/>
+      <c r="M22" s="47"/>
       <c r="N22" s="1">
         <v>3</v>
       </c>
@@ -2591,19 +2595,19 @@
       <c r="B23" s="41"/>
       <c r="C23" s="41"/>
       <c r="D23" s="41"/>
-      <c r="E23" s="49"/>
+      <c r="E23" s="50"/>
       <c r="F23" s="19">
         <v>6</v>
       </c>
       <c r="G23" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="H23" s="43"/>
-      <c r="I23" s="43"/>
-      <c r="J23" s="43"/>
-      <c r="K23" s="45"/>
-      <c r="L23" s="44"/>
-      <c r="M23" s="44"/>
+      <c r="H23" s="46"/>
+      <c r="I23" s="46"/>
+      <c r="J23" s="46"/>
+      <c r="K23" s="43"/>
+      <c r="L23" s="47"/>
+      <c r="M23" s="47"/>
       <c r="N23" s="1">
         <v>4</v>
       </c>
@@ -2616,19 +2620,19 @@
       <c r="B24" s="41"/>
       <c r="C24" s="41"/>
       <c r="D24" s="41"/>
-      <c r="E24" s="49"/>
+      <c r="E24" s="50"/>
       <c r="F24" s="19">
         <v>6</v>
       </c>
       <c r="G24" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="H24" s="43"/>
-      <c r="I24" s="43"/>
-      <c r="J24" s="43"/>
-      <c r="K24" s="45"/>
-      <c r="L24" s="44"/>
-      <c r="M24" s="44"/>
+      <c r="H24" s="46"/>
+      <c r="I24" s="46"/>
+      <c r="J24" s="46"/>
+      <c r="K24" s="43"/>
+      <c r="L24" s="47"/>
+      <c r="M24" s="47"/>
       <c r="N24" s="1">
         <v>5</v>
       </c>
@@ -2641,19 +2645,19 @@
       <c r="B25" s="41"/>
       <c r="C25" s="41"/>
       <c r="D25" s="41"/>
-      <c r="E25" s="49"/>
+      <c r="E25" s="50"/>
       <c r="F25" s="19">
         <v>6</v>
       </c>
       <c r="G25" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="H25" s="43"/>
-      <c r="I25" s="43"/>
-      <c r="J25" s="43"/>
-      <c r="K25" s="45"/>
-      <c r="L25" s="44"/>
-      <c r="M25" s="44"/>
+      <c r="H25" s="46"/>
+      <c r="I25" s="46"/>
+      <c r="J25" s="46"/>
+      <c r="K25" s="43"/>
+      <c r="L25" s="47"/>
+      <c r="M25" s="47"/>
       <c r="N25" s="1">
         <v>6</v>
       </c>
@@ -2666,19 +2670,19 @@
       <c r="B26" s="41"/>
       <c r="C26" s="41"/>
       <c r="D26" s="41"/>
-      <c r="E26" s="49"/>
+      <c r="E26" s="50"/>
       <c r="F26" s="19">
         <v>6</v>
       </c>
       <c r="G26" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="H26" s="43"/>
-      <c r="I26" s="43"/>
-      <c r="J26" s="43"/>
-      <c r="K26" s="45"/>
-      <c r="L26" s="44"/>
-      <c r="M26" s="44"/>
+      <c r="H26" s="46"/>
+      <c r="I26" s="46"/>
+      <c r="J26" s="46"/>
+      <c r="K26" s="43"/>
+      <c r="L26" s="47"/>
+      <c r="M26" s="47"/>
       <c r="N26" s="1">
         <v>7</v>
       </c>
@@ -2691,19 +2695,19 @@
       <c r="B27" s="41"/>
       <c r="C27" s="41"/>
       <c r="D27" s="41"/>
-      <c r="E27" s="49"/>
+      <c r="E27" s="50"/>
       <c r="F27" s="19">
         <v>6</v>
       </c>
       <c r="G27" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="H27" s="43"/>
-      <c r="I27" s="43"/>
-      <c r="J27" s="43"/>
-      <c r="K27" s="45"/>
-      <c r="L27" s="44"/>
-      <c r="M27" s="44"/>
+      <c r="H27" s="46"/>
+      <c r="I27" s="46"/>
+      <c r="J27" s="46"/>
+      <c r="K27" s="43"/>
+      <c r="L27" s="47"/>
+      <c r="M27" s="47"/>
       <c r="N27" s="1">
         <v>8</v>
       </c>
@@ -2716,19 +2720,19 @@
       <c r="B28" s="41"/>
       <c r="C28" s="41"/>
       <c r="D28" s="41"/>
-      <c r="E28" s="49"/>
+      <c r="E28" s="50"/>
       <c r="F28" s="19">
         <v>6</v>
       </c>
       <c r="G28" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="H28" s="43"/>
-      <c r="I28" s="43"/>
-      <c r="J28" s="43"/>
-      <c r="K28" s="45"/>
-      <c r="L28" s="44"/>
-      <c r="M28" s="44"/>
+      <c r="H28" s="46"/>
+      <c r="I28" s="46"/>
+      <c r="J28" s="46"/>
+      <c r="K28" s="43"/>
+      <c r="L28" s="47"/>
+      <c r="M28" s="47"/>
       <c r="N28" s="1">
         <v>9</v>
       </c>
@@ -2741,19 +2745,19 @@
       <c r="B29" s="41"/>
       <c r="C29" s="41"/>
       <c r="D29" s="41"/>
-      <c r="E29" s="49"/>
+      <c r="E29" s="50"/>
       <c r="F29" s="19">
         <v>6</v>
       </c>
       <c r="G29" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="H29" s="43"/>
-      <c r="I29" s="43"/>
-      <c r="J29" s="43"/>
-      <c r="K29" s="45"/>
-      <c r="L29" s="44"/>
-      <c r="M29" s="44"/>
+      <c r="H29" s="46"/>
+      <c r="I29" s="46"/>
+      <c r="J29" s="46"/>
+      <c r="K29" s="43"/>
+      <c r="L29" s="47"/>
+      <c r="M29" s="47"/>
       <c r="N29" s="1">
         <v>10</v>
       </c>
@@ -2766,19 +2770,19 @@
       <c r="B30" s="41"/>
       <c r="C30" s="41"/>
       <c r="D30" s="41"/>
-      <c r="E30" s="49"/>
+      <c r="E30" s="50"/>
       <c r="F30" s="19">
         <v>6</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="H30" s="43"/>
-      <c r="I30" s="43"/>
-      <c r="J30" s="43"/>
-      <c r="K30" s="45"/>
-      <c r="L30" s="44"/>
-      <c r="M30" s="44"/>
+      <c r="H30" s="46"/>
+      <c r="I30" s="46"/>
+      <c r="J30" s="46"/>
+      <c r="K30" s="43"/>
+      <c r="L30" s="47"/>
+      <c r="M30" s="47"/>
       <c r="N30" s="1">
         <v>11</v>
       </c>
@@ -2791,18 +2795,18 @@
       <c r="B31" s="41"/>
       <c r="C31" s="41"/>
       <c r="D31" s="41"/>
-      <c r="E31" s="49"/>
+      <c r="E31" s="50"/>
       <c r="F31" s="19">
         <v>6</v>
       </c>
       <c r="G31" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="H31" s="43"/>
-      <c r="I31" s="43"/>
-      <c r="J31" s="43"/>
-      <c r="K31" s="45"/>
-      <c r="L31" s="44"/>
+      <c r="H31" s="46"/>
+      <c r="I31" s="46"/>
+      <c r="J31" s="46"/>
+      <c r="K31" s="43"/>
+      <c r="L31" s="47"/>
       <c r="M31" s="38"/>
       <c r="N31" s="1" t="s">
         <v>180</v>
@@ -2816,18 +2820,18 @@
       <c r="B32" s="41"/>
       <c r="C32" s="41"/>
       <c r="D32" s="41"/>
-      <c r="E32" s="49"/>
+      <c r="E32" s="50"/>
       <c r="F32" s="19">
         <v>6</v>
       </c>
       <c r="G32" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="H32" s="43"/>
-      <c r="I32" s="43"/>
-      <c r="J32" s="43"/>
-      <c r="K32" s="45"/>
-      <c r="L32" s="44"/>
+      <c r="H32" s="46"/>
+      <c r="I32" s="46"/>
+      <c r="J32" s="46"/>
+      <c r="K32" s="43"/>
+      <c r="L32" s="47"/>
       <c r="M32" s="37" t="s">
         <v>162</v>
       </c>
@@ -2843,19 +2847,19 @@
       <c r="B33" s="41"/>
       <c r="C33" s="41"/>
       <c r="D33" s="41"/>
-      <c r="E33" s="49"/>
+      <c r="E33" s="50"/>
       <c r="F33" s="19">
         <v>6</v>
       </c>
       <c r="G33" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="H33" s="43"/>
-      <c r="I33" s="43"/>
-      <c r="J33" s="43"/>
-      <c r="K33" s="45"/>
-      <c r="L33" s="44"/>
-      <c r="M33" s="44"/>
+      <c r="H33" s="46"/>
+      <c r="I33" s="46"/>
+      <c r="J33" s="46"/>
+      <c r="K33" s="43"/>
+      <c r="L33" s="47"/>
+      <c r="M33" s="47"/>
       <c r="N33" s="1">
         <v>1</v>
       </c>
@@ -2868,19 +2872,19 @@
       <c r="B34" s="41"/>
       <c r="C34" s="41"/>
       <c r="D34" s="41"/>
-      <c r="E34" s="49"/>
+      <c r="E34" s="50"/>
       <c r="F34" s="19">
         <v>6</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="H34" s="43"/>
-      <c r="I34" s="43"/>
-      <c r="J34" s="43"/>
-      <c r="K34" s="45"/>
-      <c r="L34" s="44"/>
-      <c r="M34" s="44"/>
+      <c r="H34" s="46"/>
+      <c r="I34" s="46"/>
+      <c r="J34" s="46"/>
+      <c r="K34" s="43"/>
+      <c r="L34" s="47"/>
+      <c r="M34" s="47"/>
       <c r="N34" s="1">
         <v>2</v>
       </c>
@@ -2893,19 +2897,19 @@
       <c r="B35" s="41"/>
       <c r="C35" s="41"/>
       <c r="D35" s="41"/>
-      <c r="E35" s="49"/>
+      <c r="E35" s="50"/>
       <c r="F35" s="19">
         <v>6</v>
       </c>
       <c r="G35" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="H35" s="43"/>
-      <c r="I35" s="43"/>
-      <c r="J35" s="43"/>
-      <c r="K35" s="45"/>
-      <c r="L35" s="44"/>
-      <c r="M35" s="44"/>
+      <c r="H35" s="46"/>
+      <c r="I35" s="46"/>
+      <c r="J35" s="46"/>
+      <c r="K35" s="43"/>
+      <c r="L35" s="47"/>
+      <c r="M35" s="47"/>
       <c r="N35" s="1">
         <v>3</v>
       </c>
@@ -2918,18 +2922,18 @@
       <c r="B36" s="41"/>
       <c r="C36" s="41"/>
       <c r="D36" s="41"/>
-      <c r="E36" s="49"/>
+      <c r="E36" s="50"/>
       <c r="F36" s="19">
         <v>6</v>
       </c>
       <c r="G36" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="H36" s="43"/>
-      <c r="I36" s="43"/>
-      <c r="J36" s="43"/>
-      <c r="K36" s="45"/>
-      <c r="L36" s="44"/>
+      <c r="H36" s="46"/>
+      <c r="I36" s="46"/>
+      <c r="J36" s="46"/>
+      <c r="K36" s="43"/>
+      <c r="L36" s="47"/>
       <c r="M36" s="38"/>
       <c r="N36" s="1" t="s">
         <v>167</v>
@@ -2943,18 +2947,18 @@
       <c r="B37" s="41"/>
       <c r="C37" s="41"/>
       <c r="D37" s="41"/>
-      <c r="E37" s="49"/>
+      <c r="E37" s="50"/>
       <c r="F37" s="19">
         <v>6</v>
       </c>
       <c r="G37" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="H37" s="43"/>
-      <c r="I37" s="43"/>
-      <c r="J37" s="43"/>
-      <c r="K37" s="45"/>
-      <c r="L37" s="44"/>
+      <c r="H37" s="46"/>
+      <c r="I37" s="46"/>
+      <c r="J37" s="46"/>
+      <c r="K37" s="43"/>
+      <c r="L37" s="47"/>
       <c r="M37" s="37" t="s">
         <v>168</v>
       </c>
@@ -2970,19 +2974,19 @@
       <c r="B38" s="41"/>
       <c r="C38" s="41"/>
       <c r="D38" s="41"/>
-      <c r="E38" s="49"/>
+      <c r="E38" s="50"/>
       <c r="F38" s="19">
         <v>6</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="H38" s="43"/>
-      <c r="I38" s="43"/>
-      <c r="J38" s="43"/>
-      <c r="K38" s="45"/>
-      <c r="L38" s="44"/>
-      <c r="M38" s="44"/>
+      <c r="H38" s="46"/>
+      <c r="I38" s="46"/>
+      <c r="J38" s="46"/>
+      <c r="K38" s="43"/>
+      <c r="L38" s="47"/>
+      <c r="M38" s="47"/>
       <c r="N38" s="1">
         <v>1</v>
       </c>
@@ -2995,19 +2999,19 @@
       <c r="B39" s="41"/>
       <c r="C39" s="41"/>
       <c r="D39" s="41"/>
-      <c r="E39" s="49"/>
+      <c r="E39" s="50"/>
       <c r="F39" s="19">
         <v>6</v>
       </c>
       <c r="G39" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="H39" s="43"/>
-      <c r="I39" s="43"/>
-      <c r="J39" s="43"/>
-      <c r="K39" s="45"/>
-      <c r="L39" s="44"/>
-      <c r="M39" s="44"/>
+      <c r="H39" s="46"/>
+      <c r="I39" s="46"/>
+      <c r="J39" s="46"/>
+      <c r="K39" s="43"/>
+      <c r="L39" s="47"/>
+      <c r="M39" s="47"/>
       <c r="N39" s="1">
         <v>2</v>
       </c>
@@ -3020,19 +3024,19 @@
       <c r="B40" s="41"/>
       <c r="C40" s="41"/>
       <c r="D40" s="41"/>
-      <c r="E40" s="49"/>
+      <c r="E40" s="50"/>
       <c r="F40" s="19">
         <v>6</v>
       </c>
       <c r="G40" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="H40" s="43"/>
-      <c r="I40" s="43"/>
-      <c r="J40" s="43"/>
-      <c r="K40" s="45"/>
-      <c r="L40" s="44"/>
-      <c r="M40" s="44"/>
+      <c r="H40" s="46"/>
+      <c r="I40" s="46"/>
+      <c r="J40" s="46"/>
+      <c r="K40" s="43"/>
+      <c r="L40" s="47"/>
+      <c r="M40" s="47"/>
       <c r="N40" s="1">
         <v>3</v>
       </c>
@@ -3045,19 +3049,19 @@
       <c r="B41" s="41"/>
       <c r="C41" s="41"/>
       <c r="D41" s="41"/>
-      <c r="E41" s="49"/>
+      <c r="E41" s="50"/>
       <c r="F41" s="19">
         <v>6</v>
       </c>
       <c r="G41" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="H41" s="43"/>
-      <c r="I41" s="43"/>
-      <c r="J41" s="43"/>
-      <c r="K41" s="45"/>
-      <c r="L41" s="44"/>
-      <c r="M41" s="44"/>
+      <c r="H41" s="46"/>
+      <c r="I41" s="46"/>
+      <c r="J41" s="46"/>
+      <c r="K41" s="43"/>
+      <c r="L41" s="47"/>
+      <c r="M41" s="47"/>
       <c r="N41" s="1">
         <v>4</v>
       </c>
@@ -3070,19 +3074,19 @@
       <c r="B42" s="41"/>
       <c r="C42" s="41"/>
       <c r="D42" s="41"/>
-      <c r="E42" s="49"/>
+      <c r="E42" s="50"/>
       <c r="F42" s="19">
         <v>6</v>
       </c>
       <c r="G42" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="H42" s="43"/>
-      <c r="I42" s="43"/>
-      <c r="J42" s="43"/>
-      <c r="K42" s="45"/>
-      <c r="L42" s="44"/>
-      <c r="M42" s="44"/>
+      <c r="H42" s="46"/>
+      <c r="I42" s="46"/>
+      <c r="J42" s="46"/>
+      <c r="K42" s="43"/>
+      <c r="L42" s="47"/>
+      <c r="M42" s="47"/>
       <c r="N42" s="1">
         <v>5</v>
       </c>
@@ -3095,18 +3099,18 @@
       <c r="B43" s="41"/>
       <c r="C43" s="41"/>
       <c r="D43" s="41"/>
-      <c r="E43" s="49"/>
+      <c r="E43" s="50"/>
       <c r="F43" s="19">
         <v>6</v>
       </c>
       <c r="G43" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="H43" s="43"/>
-      <c r="I43" s="43"/>
-      <c r="J43" s="43"/>
-      <c r="K43" s="45"/>
-      <c r="L43" s="44"/>
+      <c r="H43" s="46"/>
+      <c r="I43" s="46"/>
+      <c r="J43" s="46"/>
+      <c r="K43" s="43"/>
+      <c r="L43" s="47"/>
       <c r="M43" s="38"/>
       <c r="N43" s="1" t="s">
         <v>175</v>
@@ -3120,18 +3124,18 @@
       <c r="B44" s="41"/>
       <c r="C44" s="41"/>
       <c r="D44" s="41"/>
-      <c r="E44" s="49"/>
+      <c r="E44" s="50"/>
       <c r="F44" s="19">
         <v>8</v>
       </c>
       <c r="G44" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="H44" s="43"/>
-      <c r="I44" s="43"/>
-      <c r="J44" s="43"/>
-      <c r="K44" s="45"/>
-      <c r="L44" s="44"/>
+      <c r="H44" s="46"/>
+      <c r="I44" s="46"/>
+      <c r="J44" s="46"/>
+      <c r="K44" s="43"/>
+      <c r="L44" s="47"/>
       <c r="M44" s="1" t="s">
         <v>176</v>
       </c>
@@ -3145,115 +3149,115 @@
       <c r="B45" s="41"/>
       <c r="C45" s="41"/>
       <c r="D45" s="41"/>
-      <c r="E45" s="49"/>
+      <c r="E45" s="50"/>
       <c r="F45" s="19">
         <v>8</v>
       </c>
       <c r="G45" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="H45" s="43"/>
-      <c r="I45" s="43"/>
-      <c r="J45" s="43"/>
-      <c r="K45" s="45"/>
-      <c r="L45" s="44"/>
+      <c r="H45" s="46"/>
+      <c r="I45" s="46"/>
+      <c r="J45" s="46"/>
+      <c r="K45" s="43"/>
+      <c r="L45" s="47"/>
     </row>
     <row r="46" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="41"/>
       <c r="B46" s="41"/>
       <c r="C46" s="41"/>
       <c r="D46" s="41"/>
-      <c r="E46" s="49"/>
+      <c r="E46" s="50"/>
       <c r="F46" s="19">
         <v>6</v>
       </c>
       <c r="G46" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="H46" s="43"/>
-      <c r="I46" s="43"/>
-      <c r="J46" s="43"/>
-      <c r="K46" s="45"/>
-      <c r="L46" s="44"/>
+      <c r="H46" s="46"/>
+      <c r="I46" s="46"/>
+      <c r="J46" s="46"/>
+      <c r="K46" s="43"/>
+      <c r="L46" s="47"/>
     </row>
     <row r="47" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="41"/>
       <c r="B47" s="41"/>
       <c r="C47" s="41"/>
       <c r="D47" s="41"/>
-      <c r="E47" s="49"/>
+      <c r="E47" s="50"/>
       <c r="F47" s="19">
         <v>6</v>
       </c>
       <c r="G47" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="H47" s="43"/>
-      <c r="I47" s="43"/>
-      <c r="J47" s="43"/>
-      <c r="K47" s="45"/>
-      <c r="L47" s="44"/>
+      <c r="H47" s="46"/>
+      <c r="I47" s="46"/>
+      <c r="J47" s="46"/>
+      <c r="K47" s="43"/>
+      <c r="L47" s="47"/>
     </row>
     <row r="48" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="41"/>
       <c r="B48" s="41"/>
       <c r="C48" s="41"/>
       <c r="D48" s="41"/>
-      <c r="E48" s="49"/>
+      <c r="E48" s="50"/>
       <c r="F48" s="19">
         <v>6</v>
       </c>
       <c r="G48" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="H48" s="43"/>
-      <c r="I48" s="43"/>
-      <c r="J48" s="43"/>
-      <c r="K48" s="45"/>
-      <c r="L48" s="44"/>
+      <c r="H48" s="46"/>
+      <c r="I48" s="46"/>
+      <c r="J48" s="46"/>
+      <c r="K48" s="43"/>
+      <c r="L48" s="47"/>
     </row>
     <row r="49" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="41"/>
       <c r="B49" s="41"/>
       <c r="C49" s="41"/>
       <c r="D49" s="41"/>
-      <c r="E49" s="49"/>
+      <c r="E49" s="50"/>
       <c r="F49" s="19">
         <v>6</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="H49" s="43"/>
-      <c r="I49" s="43"/>
-      <c r="J49" s="43"/>
-      <c r="K49" s="45"/>
-      <c r="L49" s="44"/>
+      <c r="H49" s="46"/>
+      <c r="I49" s="46"/>
+      <c r="J49" s="46"/>
+      <c r="K49" s="43"/>
+      <c r="L49" s="47"/>
     </row>
     <row r="50" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="41"/>
       <c r="B50" s="41"/>
       <c r="C50" s="41"/>
       <c r="D50" s="41"/>
-      <c r="E50" s="49"/>
+      <c r="E50" s="50"/>
       <c r="F50" s="19">
         <v>6</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="H50" s="43"/>
-      <c r="I50" s="43"/>
-      <c r="J50" s="43"/>
-      <c r="K50" s="45"/>
-      <c r="L50" s="44"/>
+      <c r="H50" s="46"/>
+      <c r="I50" s="46"/>
+      <c r="J50" s="46"/>
+      <c r="K50" s="43"/>
+      <c r="L50" s="47"/>
     </row>
     <row r="51" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="16"/>
       <c r="B51" s="16"/>
       <c r="C51" s="16"/>
       <c r="D51" s="16"/>
-      <c r="E51" s="50"/>
+      <c r="E51" s="51"/>
       <c r="F51" s="19">
         <v>6</v>
       </c>
@@ -3279,7 +3283,7 @@
       <c r="D52" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E52" s="30" t="s">
+      <c r="E52" s="31" t="s">
         <v>38</v>
       </c>
       <c r="F52" s="1">
@@ -3309,7 +3313,7 @@
       <c r="D53" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E53" s="30"/>
+      <c r="E53" s="31"/>
       <c r="F53" s="1">
         <v>238</v>
       </c>
@@ -3337,7 +3341,7 @@
       <c r="D54" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E54" s="30"/>
+      <c r="E54" s="31"/>
       <c r="F54" s="1">
         <v>238</v>
       </c>
@@ -3365,7 +3369,7 @@
       <c r="D55" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E55" s="30"/>
+      <c r="E55" s="31"/>
       <c r="F55" s="1">
         <v>238</v>
       </c>
@@ -3393,7 +3397,7 @@
       <c r="D56" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E56" s="30"/>
+      <c r="E56" s="31"/>
       <c r="F56" s="1">
         <v>238</v>
       </c>
@@ -3421,7 +3425,7 @@
       <c r="D57" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E57" s="30"/>
+      <c r="E57" s="31"/>
       <c r="F57" s="1">
         <v>238</v>
       </c>
@@ -3449,7 +3453,7 @@
       <c r="D58" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E58" s="30"/>
+      <c r="E58" s="31"/>
       <c r="F58" s="1">
         <v>238</v>
       </c>
@@ -3477,7 +3481,7 @@
       <c r="D59" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E59" s="30"/>
+      <c r="E59" s="31"/>
       <c r="F59" s="1">
         <v>238</v>
       </c>
@@ -3506,7 +3510,7 @@
       <c r="D60" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E60" s="30"/>
+      <c r="E60" s="31"/>
       <c r="F60" s="1">
         <v>238</v>
       </c>
@@ -3534,7 +3538,7 @@
       <c r="D61" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E61" s="30"/>
+      <c r="E61" s="31"/>
       <c r="F61" s="1">
         <v>238</v>
       </c>
@@ -3563,7 +3567,7 @@
       <c r="D62" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E62" s="30"/>
+      <c r="E62" s="31"/>
       <c r="F62" s="1">
         <v>238</v>
       </c>
@@ -3591,7 +3595,7 @@
       <c r="D63" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E63" s="30"/>
+      <c r="E63" s="31"/>
       <c r="F63" s="1">
         <v>238</v>
       </c>
@@ -3619,7 +3623,7 @@
       <c r="D64" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E64" s="30"/>
+      <c r="E64" s="31"/>
       <c r="F64" s="1">
         <v>238</v>
       </c>
@@ -3647,7 +3651,7 @@
       <c r="D65" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E65" s="30"/>
+      <c r="E65" s="31"/>
       <c r="F65" s="1">
         <v>238</v>
       </c>
@@ -3676,7 +3680,7 @@
       <c r="D66" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E66" s="30"/>
+      <c r="E66" s="31"/>
       <c r="F66" s="1">
         <v>238</v>
       </c>
@@ -3704,7 +3708,7 @@
       <c r="D67" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E67" s="30"/>
+      <c r="E67" s="31"/>
       <c r="F67" s="1">
         <v>238</v>
       </c>
@@ -3732,7 +3736,7 @@
       <c r="D68" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E68" s="30"/>
+      <c r="E68" s="31"/>
       <c r="F68" s="1">
         <v>238</v>
       </c>
@@ -3760,7 +3764,7 @@
       <c r="D69" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E69" s="30"/>
+      <c r="E69" s="31"/>
       <c r="F69" s="1">
         <v>238</v>
       </c>
@@ -3788,7 +3792,7 @@
       <c r="D70" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="E70" s="30"/>
+      <c r="E70" s="31"/>
       <c r="F70" s="1">
         <v>238</v>
       </c>
@@ -3816,7 +3820,7 @@
       <c r="D71" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E71" s="30"/>
+      <c r="E71" s="31"/>
       <c r="F71" s="1">
         <v>238</v>
       </c>
@@ -3844,7 +3848,7 @@
       <c r="D72" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E72" s="30"/>
+      <c r="E72" s="31"/>
       <c r="F72" s="1">
         <v>238</v>
       </c>
@@ -3872,7 +3876,7 @@
       <c r="D73" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E73" s="30"/>
+      <c r="E73" s="31"/>
       <c r="F73" s="1">
         <v>238</v>
       </c>
@@ -3900,7 +3904,7 @@
       <c r="D74" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="E74" s="30"/>
+      <c r="E74" s="31"/>
       <c r="F74" s="1">
         <v>238</v>
       </c>
@@ -3928,7 +3932,7 @@
       <c r="D75" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E75" s="30"/>
+      <c r="E75" s="31"/>
       <c r="F75" s="1">
         <v>238</v>
       </c>
@@ -3956,7 +3960,7 @@
       <c r="D76" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E76" s="30"/>
+      <c r="E76" s="31"/>
       <c r="F76" s="1">
         <v>238</v>
       </c>
@@ -3984,7 +3988,7 @@
       <c r="D77" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="E77" s="30"/>
+      <c r="E77" s="31"/>
       <c r="F77" s="1">
         <v>238</v>
       </c>
@@ -4012,7 +4016,7 @@
       <c r="D78" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="E78" s="30"/>
+      <c r="E78" s="31"/>
       <c r="F78" s="1">
         <v>238</v>
       </c>
@@ -4040,7 +4044,7 @@
       <c r="D79" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E79" s="30"/>
+      <c r="E79" s="31"/>
       <c r="F79" s="1">
         <v>238</v>
       </c>
@@ -4068,7 +4072,7 @@
       <c r="D80" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="E80" s="30"/>
+      <c r="E80" s="31"/>
       <c r="F80" s="1">
         <v>238</v>
       </c>
@@ -4096,7 +4100,7 @@
       <c r="D81" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="E81" s="30"/>
+      <c r="E81" s="31"/>
       <c r="F81" s="1">
         <v>238</v>
       </c>
@@ -4124,7 +4128,7 @@
       <c r="D82" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="E82" s="30"/>
+      <c r="E82" s="31"/>
       <c r="F82" s="1">
         <v>238</v>
       </c>
@@ -4152,7 +4156,7 @@
       <c r="D83" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E83" s="30"/>
+      <c r="E83" s="31"/>
       <c r="F83" s="1">
         <v>238</v>
       </c>
@@ -4180,7 +4184,7 @@
       <c r="D84" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="E84" s="30"/>
+      <c r="E84" s="31"/>
       <c r="F84" s="1">
         <v>238</v>
       </c>
@@ -4208,7 +4212,7 @@
       <c r="D85" s="1">
         <v>23</v>
       </c>
-      <c r="E85" s="30"/>
+      <c r="E85" s="31"/>
       <c r="F85" s="1">
         <v>238</v>
       </c>
@@ -4236,7 +4240,7 @@
       <c r="D86" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E86" s="30"/>
+      <c r="E86" s="31"/>
       <c r="F86" s="1">
         <v>238</v>
       </c>
@@ -4264,7 +4268,7 @@
       <c r="D87" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E87" s="30"/>
+      <c r="E87" s="31"/>
       <c r="F87" s="1">
         <v>238</v>
       </c>
@@ -4309,18 +4313,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="G2:G3"/>
-    <mergeCell ref="A4:A16"/>
-    <mergeCell ref="B4:B16"/>
-    <mergeCell ref="C4:C16"/>
-    <mergeCell ref="C18:C50"/>
-    <mergeCell ref="B18:B50"/>
-    <mergeCell ref="A18:A50"/>
+    <mergeCell ref="D18:D50"/>
+    <mergeCell ref="J18:J50"/>
+    <mergeCell ref="L18:L50"/>
+    <mergeCell ref="M19:M31"/>
+    <mergeCell ref="M32:M36"/>
+    <mergeCell ref="M37:M43"/>
     <mergeCell ref="E52:E87"/>
     <mergeCell ref="K5:K16"/>
     <mergeCell ref="K2:K3"/>
@@ -4332,12 +4330,18 @@
     <mergeCell ref="I4:I16"/>
     <mergeCell ref="E5:E16"/>
     <mergeCell ref="E18:E51"/>
-    <mergeCell ref="D18:D50"/>
-    <mergeCell ref="J18:J50"/>
-    <mergeCell ref="L18:L50"/>
-    <mergeCell ref="M19:M31"/>
-    <mergeCell ref="M32:M36"/>
-    <mergeCell ref="M37:M43"/>
+    <mergeCell ref="A4:A16"/>
+    <mergeCell ref="B4:B16"/>
+    <mergeCell ref="C4:C16"/>
+    <mergeCell ref="C18:C50"/>
+    <mergeCell ref="B18:B50"/>
+    <mergeCell ref="A18:A50"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="G2:G3"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A4:E4 K60 A18:E18 D5:D17 A2:K2 K52:K56 A3:F3 H3:J3 K17 K4:K5 E52 D52:D84 D86:D88 A52:C88 K62 J4:J18 J52:J88">

--- a/doc/5、开发文档/DFDL33-SH8619 协议转换单元DLT64点表.xlsx
+++ b/doc/5、开发文档/DFDL33-SH8619 协议转换单元DLT64点表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Project\SVN\DFDL33-SH8619\doc\5、开发文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9764043C-622F-4474-8A47-C40767D51AAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{818274B1-3CFE-4DF9-8D89-753D233C5A20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="2775" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="参变量" sheetId="4" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="489" uniqueCount="221">
   <si>
     <t>00</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -843,10 +843,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>维度</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>高度</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -892,6 +888,14 @@
   </si>
   <si>
     <t>80</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>XXXX.XX</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>纬度</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1129,19 +1133,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1165,35 +1169,35 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1554,13 +1558,13 @@
       <c r="K1" s="13"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="30" t="s">
+      <c r="A2" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="30"/>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="31" t="s">
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="30" t="s">
         <v>3</v>
       </c>
       <c r="F2" s="34" t="s">
@@ -1569,14 +1573,14 @@
       <c r="G2" s="37" t="s">
         <v>137</v>
       </c>
-      <c r="H2" s="31" t="s">
+      <c r="H2" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="31"/>
+      <c r="I2" s="30"/>
       <c r="J2" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="32" t="s">
+      <c r="K2" s="31" t="s">
         <v>144</v>
       </c>
     </row>
@@ -1593,7 +1597,7 @@
       <c r="D3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="31"/>
+      <c r="E3" s="30"/>
       <c r="F3" s="34"/>
       <c r="G3" s="38"/>
       <c r="H3" s="1" t="s">
@@ -1603,16 +1607,16 @@
         <v>11</v>
       </c>
       <c r="J3" s="39"/>
-      <c r="K3" s="33"/>
+      <c r="K3" s="32"/>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="30" t="s">
+      <c r="A4" s="33" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="33" t="s">
         <v>184</v>
       </c>
       <c r="D4" s="2" t="s">
@@ -1625,10 +1629,10 @@
         <v>186</v>
       </c>
       <c r="G4" s="21"/>
-      <c r="H4" s="31" t="s">
+      <c r="H4" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="I4" s="31" t="s">
+      <c r="I4" s="30" t="s">
         <v>14</v>
       </c>
       <c r="J4" s="1" t="s">
@@ -1637,17 +1641,17 @@
       <c r="K4" s="29"/>
     </row>
     <row r="5" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="30"/>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
+      <c r="A5" s="33"/>
+      <c r="B5" s="33"/>
+      <c r="C5" s="33"/>
       <c r="D5" s="2" t="s">
         <v>23</v>
       </c>
       <c r="E5" s="36"/>
       <c r="F5" s="34"/>
       <c r="G5" s="21"/>
-      <c r="H5" s="31"/>
-      <c r="I5" s="31"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
       <c r="J5" s="1" t="s">
         <v>188</v>
       </c>
@@ -1656,26 +1660,26 @@
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="30"/>
-      <c r="B6" s="30"/>
-      <c r="C6" s="30"/>
+      <c r="A6" s="33"/>
+      <c r="B6" s="33"/>
+      <c r="C6" s="33"/>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="36"/>
       <c r="F6" s="34"/>
       <c r="G6" s="21"/>
-      <c r="H6" s="31"/>
-      <c r="I6" s="31"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="30"/>
       <c r="J6" s="1" t="s">
         <v>189</v>
       </c>
       <c r="K6" s="35"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="30"/>
-      <c r="B7" s="30"/>
-      <c r="C7" s="30"/>
+      <c r="A7" s="33"/>
+      <c r="B7" s="33"/>
+      <c r="C7" s="33"/>
       <c r="D7" s="2" t="s">
         <v>16</v>
       </c>
@@ -1684,17 +1688,17 @@
       <c r="G7" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="H7" s="31"/>
-      <c r="I7" s="31"/>
+      <c r="H7" s="30"/>
+      <c r="I7" s="30"/>
       <c r="J7" s="1" t="s">
         <v>190</v>
       </c>
       <c r="K7" s="35"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="30"/>
-      <c r="B8" s="30"/>
-      <c r="C8" s="30"/>
+      <c r="A8" s="33"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="33"/>
       <c r="D8" s="2" t="s">
         <v>12</v>
       </c>
@@ -1703,59 +1707,59 @@
       <c r="G8" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="H8" s="31"/>
-      <c r="I8" s="31"/>
+      <c r="H8" s="30"/>
+      <c r="I8" s="30"/>
       <c r="J8" s="1" t="s">
         <v>191</v>
       </c>
       <c r="K8" s="35"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="30"/>
-      <c r="B9" s="30"/>
-      <c r="C9" s="30"/>
+      <c r="A9" s="33"/>
+      <c r="B9" s="33"/>
+      <c r="C9" s="33"/>
       <c r="D9" s="2" t="s">
         <v>20</v>
       </c>
       <c r="E9" s="36"/>
       <c r="F9" s="34"/>
       <c r="G9" s="1"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="31"/>
+      <c r="H9" s="30"/>
+      <c r="I9" s="30"/>
       <c r="J9" s="1" t="s">
         <v>192</v>
       </c>
       <c r="K9" s="35"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="30"/>
-      <c r="B10" s="30"/>
-      <c r="C10" s="30"/>
+      <c r="A10" s="33"/>
+      <c r="B10" s="33"/>
+      <c r="C10" s="33"/>
       <c r="D10" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E10" s="36"/>
       <c r="F10" s="34"/>
       <c r="G10" s="1"/>
-      <c r="H10" s="31"/>
-      <c r="I10" s="31"/>
+      <c r="H10" s="30"/>
+      <c r="I10" s="30"/>
       <c r="J10" s="1" t="s">
         <v>193</v>
       </c>
       <c r="K10" s="35"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="30"/>
-      <c r="B11" s="30"/>
-      <c r="C11" s="30"/>
+      <c r="A11" s="33"/>
+      <c r="B11" s="33"/>
+      <c r="C11" s="33"/>
       <c r="D11" s="2" t="s">
         <v>21</v>
       </c>
       <c r="E11" s="36"/>
       <c r="F11" s="34"/>
       <c r="G11" s="1"/>
-      <c r="H11" s="31"/>
-      <c r="I11" s="31"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
       <c r="J11" s="1" t="s">
         <v>194</v>
       </c>
@@ -1775,7 +1779,7 @@
         <v>0</v>
       </c>
       <c r="E13" s="27" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F13" s="27">
         <v>2</v>
@@ -1791,7 +1795,7 @@
         <v>199</v>
       </c>
       <c r="K13" s="28" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
@@ -1822,7 +1826,7 @@
         <v>200</v>
       </c>
       <c r="K14" s="28" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
@@ -1853,7 +1857,7 @@
         <v>201</v>
       </c>
       <c r="K15" s="28" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
@@ -1884,7 +1888,7 @@
         <v>202</v>
       </c>
       <c r="K16" s="28" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
@@ -1912,34 +1916,36 @@
         <v>14</v>
       </c>
       <c r="J17" s="27" t="s">
+        <v>216</v>
+      </c>
+      <c r="K17" s="28" t="s">
         <v>217</v>
       </c>
-      <c r="K17" s="28" t="s">
-        <v>218</v>
-      </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="30" t="s">
+      <c r="A19" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="30" t="s">
+      <c r="B19" s="33" t="s">
         <v>183</v>
       </c>
-      <c r="C19" s="30" t="s">
+      <c r="C19" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="D19" s="30" t="s">
+      <c r="D19" s="33" t="s">
         <v>203</v>
       </c>
       <c r="E19" s="27" t="s">
         <v>205</v>
       </c>
-      <c r="F19" s="27"/>
+      <c r="F19" s="27">
+        <v>4</v>
+      </c>
       <c r="G19" s="27"/>
-      <c r="H19" s="31" t="s">
-        <v>215</v>
-      </c>
-      <c r="I19" s="31" t="s">
+      <c r="H19" s="30" t="s">
+        <v>214</v>
+      </c>
+      <c r="I19" s="30" t="s">
         <v>14</v>
       </c>
       <c r="J19" s="27" t="s">
@@ -1948,36 +1954,40 @@
       <c r="K19" s="28"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="30"/>
-      <c r="B20" s="30"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
+      <c r="A20" s="33"/>
+      <c r="B20" s="33"/>
+      <c r="C20" s="33"/>
+      <c r="D20" s="33"/>
       <c r="E20" s="27" t="s">
         <v>204</v>
       </c>
-      <c r="F20" s="27"/>
+      <c r="F20" s="27">
+        <v>4</v>
+      </c>
       <c r="G20" s="27"/>
-      <c r="H20" s="31"/>
-      <c r="I20" s="31"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
       <c r="J20" s="27" t="s">
+        <v>220</v>
+      </c>
+      <c r="K20" s="28"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="33"/>
+      <c r="B21" s="33"/>
+      <c r="C21" s="33"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="27" t="s">
+        <v>219</v>
+      </c>
+      <c r="F21" s="27">
+        <v>3</v>
+      </c>
+      <c r="G21" s="27"/>
+      <c r="H21" s="30"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="27" t="s">
         <v>207</v>
-      </c>
-      <c r="K20" s="28"/>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="30"/>
-      <c r="B21" s="30"/>
-      <c r="C21" s="30"/>
-      <c r="D21" s="30"/>
-      <c r="E21" s="27" t="s">
-        <v>204</v>
-      </c>
-      <c r="F21" s="27"/>
-      <c r="G21" s="27"/>
-      <c r="H21" s="31"/>
-      <c r="I21" s="31"/>
-      <c r="J21" s="27" t="s">
-        <v>208</v>
       </c>
       <c r="K21" s="28"/>
     </row>
@@ -1986,7 +1996,7 @@
         <v>1</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C23" s="26" t="s">
         <v>0</v>
@@ -1995,23 +2005,28 @@
         <v>23</v>
       </c>
       <c r="E23" s="27" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F23" s="27">
         <v>32</v>
       </c>
       <c r="G23" s="27"/>
       <c r="H23" s="27" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="I23" s="27"/>
       <c r="J23" s="27" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="K23" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="21">
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="C19:C21"/>
+    <mergeCell ref="D19:D21"/>
+    <mergeCell ref="H19:H21"/>
     <mergeCell ref="I19:I21"/>
     <mergeCell ref="K2:K3"/>
     <mergeCell ref="A4:A11"/>
@@ -2028,11 +2043,6 @@
     <mergeCell ref="G2:G3"/>
     <mergeCell ref="H2:I2"/>
     <mergeCell ref="J2:J3"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="B19:B21"/>
-    <mergeCell ref="C19:C21"/>
-    <mergeCell ref="D19:D21"/>
-    <mergeCell ref="H19:H21"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A19:D19">
@@ -2135,13 +2145,13 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="30" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31" t="s">
+      <c r="B2" s="30"/>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30" t="s">
         <v>3</v>
       </c>
       <c r="F2" s="34" t="s">
@@ -2150,14 +2160,14 @@
       <c r="G2" s="37" t="s">
         <v>137</v>
       </c>
-      <c r="H2" s="31" t="s">
+      <c r="H2" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="31"/>
+      <c r="I2" s="30"/>
       <c r="J2" s="39" t="s">
         <v>5</v>
       </c>
-      <c r="K2" s="32" t="s">
+      <c r="K2" s="31" t="s">
         <v>144</v>
       </c>
     </row>
@@ -2174,7 +2184,7 @@
       <c r="D3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="31"/>
+      <c r="E3" s="30"/>
       <c r="F3" s="34"/>
       <c r="G3" s="38"/>
       <c r="H3" s="1" t="s">
@@ -2184,7 +2194,7 @@
         <v>11</v>
       </c>
       <c r="J3" s="39"/>
-      <c r="K3" s="33"/>
+      <c r="K3" s="32"/>
     </row>
     <row r="4" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="40" t="s">
@@ -2206,10 +2216,10 @@
         <v>45</v>
       </c>
       <c r="G4" s="9"/>
-      <c r="H4" s="45" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="45" t="s">
+      <c r="H4" s="42" t="s">
+        <v>14</v>
+      </c>
+      <c r="I4" s="42" t="s">
         <v>14</v>
       </c>
       <c r="J4" s="1" t="s">
@@ -2224,17 +2234,17 @@
       <c r="D5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="49" t="s">
+      <c r="E5" s="48" t="s">
         <v>136</v>
       </c>
-      <c r="F5" s="47"/>
+      <c r="F5" s="44"/>
       <c r="G5" s="10"/>
-      <c r="H5" s="46"/>
-      <c r="I5" s="46"/>
+      <c r="H5" s="43"/>
+      <c r="I5" s="43"/>
       <c r="J5" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="K5" s="43" t="s">
+      <c r="K5" s="45" t="s">
         <v>143</v>
       </c>
     </row>
@@ -2245,15 +2255,15 @@
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="50"/>
-      <c r="F6" s="47"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="44"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="46"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
       <c r="J6" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="K6" s="43"/>
+      <c r="K6" s="45"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="41"/>
@@ -2262,15 +2272,15 @@
       <c r="D7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="50"/>
-      <c r="F7" s="47"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="44"/>
       <c r="G7" s="10"/>
-      <c r="H7" s="46"/>
-      <c r="I7" s="46"/>
+      <c r="H7" s="43"/>
+      <c r="I7" s="43"/>
       <c r="J7" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="K7" s="43"/>
+      <c r="K7" s="45"/>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="41"/>
@@ -2279,17 +2289,17 @@
       <c r="D8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="50"/>
-      <c r="F8" s="47"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="44"/>
       <c r="G8" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="H8" s="46"/>
-      <c r="I8" s="46"/>
+      <c r="H8" s="43"/>
+      <c r="I8" s="43"/>
       <c r="J8" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="K8" s="43"/>
+      <c r="K8" s="45"/>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="41"/>
@@ -2298,17 +2308,17 @@
       <c r="D9" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="50"/>
-      <c r="F9" s="47"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="44"/>
       <c r="G9" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="H9" s="46"/>
-      <c r="I9" s="46"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
       <c r="J9" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="K9" s="43"/>
+      <c r="K9" s="45"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A10" s="41"/>
@@ -2317,17 +2327,17 @@
       <c r="D10" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E10" s="50"/>
-      <c r="F10" s="47"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="44"/>
       <c r="G10" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="H10" s="46"/>
-      <c r="I10" s="46"/>
+      <c r="H10" s="43"/>
+      <c r="I10" s="43"/>
       <c r="J10" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="K10" s="43"/>
+      <c r="K10" s="45"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="41"/>
@@ -2336,17 +2346,17 @@
       <c r="D11" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="50"/>
-      <c r="F11" s="47"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="44"/>
       <c r="G11" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="H11" s="46"/>
-      <c r="I11" s="46"/>
+      <c r="H11" s="43"/>
+      <c r="I11" s="43"/>
       <c r="J11" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="K11" s="43"/>
+      <c r="K11" s="45"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="41"/>
@@ -2355,15 +2365,15 @@
       <c r="D12" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E12" s="50"/>
-      <c r="F12" s="47"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="44"/>
       <c r="G12" s="10"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="46"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="43"/>
       <c r="J12" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="K12" s="43"/>
+      <c r="K12" s="45"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="41"/>
@@ -2372,15 +2382,15 @@
       <c r="D13" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E13" s="50"/>
-      <c r="F13" s="47"/>
+      <c r="E13" s="49"/>
+      <c r="F13" s="44"/>
       <c r="G13" s="10"/>
-      <c r="H13" s="46"/>
-      <c r="I13" s="46"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="43"/>
       <c r="J13" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="K13" s="43"/>
+      <c r="K13" s="45"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="41"/>
@@ -2389,15 +2399,15 @@
       <c r="D14" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="50"/>
-      <c r="F14" s="47"/>
+      <c r="E14" s="49"/>
+      <c r="F14" s="44"/>
       <c r="G14" s="10"/>
-      <c r="H14" s="46"/>
-      <c r="I14" s="46"/>
+      <c r="H14" s="43"/>
+      <c r="I14" s="43"/>
       <c r="J14" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="K14" s="43"/>
+      <c r="K14" s="45"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A15" s="41"/>
@@ -2406,32 +2416,32 @@
       <c r="D15" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E15" s="50"/>
-      <c r="F15" s="47"/>
+      <c r="E15" s="49"/>
+      <c r="F15" s="44"/>
       <c r="G15" s="10"/>
-      <c r="H15" s="46"/>
-      <c r="I15" s="46"/>
+      <c r="H15" s="43"/>
+      <c r="I15" s="43"/>
       <c r="J15" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="K15" s="43"/>
+      <c r="K15" s="45"/>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A16" s="42"/>
-      <c r="B16" s="42"/>
-      <c r="C16" s="42"/>
+      <c r="A16" s="51"/>
+      <c r="B16" s="51"/>
+      <c r="C16" s="51"/>
       <c r="D16" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E16" s="51"/>
-      <c r="F16" s="47"/>
+      <c r="E16" s="50"/>
+      <c r="F16" s="44"/>
       <c r="G16" s="10"/>
-      <c r="H16" s="48"/>
-      <c r="I16" s="48"/>
+      <c r="H16" s="47"/>
+      <c r="I16" s="47"/>
       <c r="J16" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="K16" s="43"/>
+      <c r="K16" s="45"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A17" s="7"/>
@@ -2456,7 +2466,7 @@
       <c r="D18" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="E18" s="49" t="s">
+      <c r="E18" s="48" t="s">
         <v>178</v>
       </c>
       <c r="F18" s="18">
@@ -2465,16 +2475,16 @@
       <c r="G18" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="H18" s="45" t="s">
+      <c r="H18" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="I18" s="45" t="s">
+      <c r="I18" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="J18" s="45" t="s">
+      <c r="J18" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="K18" s="44" t="s">
+      <c r="K18" s="46" t="s">
         <v>182</v>
       </c>
       <c r="L18" s="37"/>
@@ -2493,18 +2503,18 @@
       <c r="B19" s="41"/>
       <c r="C19" s="41"/>
       <c r="D19" s="41"/>
-      <c r="E19" s="50"/>
+      <c r="E19" s="49"/>
       <c r="F19" s="19">
         <v>2</v>
       </c>
       <c r="G19" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="H19" s="46"/>
-      <c r="I19" s="46"/>
-      <c r="J19" s="46"/>
-      <c r="K19" s="43"/>
-      <c r="L19" s="47"/>
+      <c r="H19" s="43"/>
+      <c r="I19" s="43"/>
+      <c r="J19" s="43"/>
+      <c r="K19" s="45"/>
+      <c r="L19" s="44"/>
       <c r="M19" s="37" t="s">
         <v>150</v>
       </c>
@@ -2520,19 +2530,19 @@
       <c r="B20" s="41"/>
       <c r="C20" s="41"/>
       <c r="D20" s="41"/>
-      <c r="E20" s="50"/>
+      <c r="E20" s="49"/>
       <c r="F20" s="19">
         <v>14</v>
       </c>
       <c r="G20" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="H20" s="46"/>
-      <c r="I20" s="46"/>
-      <c r="J20" s="46"/>
-      <c r="K20" s="43"/>
-      <c r="L20" s="47"/>
-      <c r="M20" s="47"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="43"/>
+      <c r="J20" s="43"/>
+      <c r="K20" s="45"/>
+      <c r="L20" s="44"/>
+      <c r="M20" s="44"/>
       <c r="N20" s="1">
         <v>1</v>
       </c>
@@ -2545,19 +2555,19 @@
       <c r="B21" s="41"/>
       <c r="C21" s="41"/>
       <c r="D21" s="41"/>
-      <c r="E21" s="50"/>
+      <c r="E21" s="49"/>
       <c r="F21" s="19">
         <v>6</v>
       </c>
       <c r="G21" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="H21" s="46"/>
-      <c r="I21" s="46"/>
-      <c r="J21" s="46"/>
-      <c r="K21" s="43"/>
-      <c r="L21" s="47"/>
-      <c r="M21" s="47"/>
+      <c r="H21" s="43"/>
+      <c r="I21" s="43"/>
+      <c r="J21" s="43"/>
+      <c r="K21" s="45"/>
+      <c r="L21" s="44"/>
+      <c r="M21" s="44"/>
       <c r="N21" s="1">
         <v>2</v>
       </c>
@@ -2570,19 +2580,19 @@
       <c r="B22" s="41"/>
       <c r="C22" s="41"/>
       <c r="D22" s="41"/>
-      <c r="E22" s="50"/>
+      <c r="E22" s="49"/>
       <c r="F22" s="19">
         <v>6</v>
       </c>
       <c r="G22" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="H22" s="46"/>
-      <c r="I22" s="46"/>
-      <c r="J22" s="46"/>
-      <c r="K22" s="43"/>
-      <c r="L22" s="47"/>
-      <c r="M22" s="47"/>
+      <c r="H22" s="43"/>
+      <c r="I22" s="43"/>
+      <c r="J22" s="43"/>
+      <c r="K22" s="45"/>
+      <c r="L22" s="44"/>
+      <c r="M22" s="44"/>
       <c r="N22" s="1">
         <v>3</v>
       </c>
@@ -2595,19 +2605,19 @@
       <c r="B23" s="41"/>
       <c r="C23" s="41"/>
       <c r="D23" s="41"/>
-      <c r="E23" s="50"/>
+      <c r="E23" s="49"/>
       <c r="F23" s="19">
         <v>6</v>
       </c>
       <c r="G23" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="H23" s="46"/>
-      <c r="I23" s="46"/>
-      <c r="J23" s="46"/>
-      <c r="K23" s="43"/>
-      <c r="L23" s="47"/>
-      <c r="M23" s="47"/>
+      <c r="H23" s="43"/>
+      <c r="I23" s="43"/>
+      <c r="J23" s="43"/>
+      <c r="K23" s="45"/>
+      <c r="L23" s="44"/>
+      <c r="M23" s="44"/>
       <c r="N23" s="1">
         <v>4</v>
       </c>
@@ -2620,19 +2630,19 @@
       <c r="B24" s="41"/>
       <c r="C24" s="41"/>
       <c r="D24" s="41"/>
-      <c r="E24" s="50"/>
+      <c r="E24" s="49"/>
       <c r="F24" s="19">
         <v>6</v>
       </c>
       <c r="G24" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="H24" s="46"/>
-      <c r="I24" s="46"/>
-      <c r="J24" s="46"/>
-      <c r="K24" s="43"/>
-      <c r="L24" s="47"/>
-      <c r="M24" s="47"/>
+      <c r="H24" s="43"/>
+      <c r="I24" s="43"/>
+      <c r="J24" s="43"/>
+      <c r="K24" s="45"/>
+      <c r="L24" s="44"/>
+      <c r="M24" s="44"/>
       <c r="N24" s="1">
         <v>5</v>
       </c>
@@ -2645,19 +2655,19 @@
       <c r="B25" s="41"/>
       <c r="C25" s="41"/>
       <c r="D25" s="41"/>
-      <c r="E25" s="50"/>
+      <c r="E25" s="49"/>
       <c r="F25" s="19">
         <v>6</v>
       </c>
       <c r="G25" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="H25" s="46"/>
-      <c r="I25" s="46"/>
-      <c r="J25" s="46"/>
-      <c r="K25" s="43"/>
-      <c r="L25" s="47"/>
-      <c r="M25" s="47"/>
+      <c r="H25" s="43"/>
+      <c r="I25" s="43"/>
+      <c r="J25" s="43"/>
+      <c r="K25" s="45"/>
+      <c r="L25" s="44"/>
+      <c r="M25" s="44"/>
       <c r="N25" s="1">
         <v>6</v>
       </c>
@@ -2670,19 +2680,19 @@
       <c r="B26" s="41"/>
       <c r="C26" s="41"/>
       <c r="D26" s="41"/>
-      <c r="E26" s="50"/>
+      <c r="E26" s="49"/>
       <c r="F26" s="19">
         <v>6</v>
       </c>
       <c r="G26" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="H26" s="46"/>
-      <c r="I26" s="46"/>
-      <c r="J26" s="46"/>
-      <c r="K26" s="43"/>
-      <c r="L26" s="47"/>
-      <c r="M26" s="47"/>
+      <c r="H26" s="43"/>
+      <c r="I26" s="43"/>
+      <c r="J26" s="43"/>
+      <c r="K26" s="45"/>
+      <c r="L26" s="44"/>
+      <c r="M26" s="44"/>
       <c r="N26" s="1">
         <v>7</v>
       </c>
@@ -2695,19 +2705,19 @@
       <c r="B27" s="41"/>
       <c r="C27" s="41"/>
       <c r="D27" s="41"/>
-      <c r="E27" s="50"/>
+      <c r="E27" s="49"/>
       <c r="F27" s="19">
         <v>6</v>
       </c>
       <c r="G27" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="H27" s="46"/>
-      <c r="I27" s="46"/>
-      <c r="J27" s="46"/>
-      <c r="K27" s="43"/>
-      <c r="L27" s="47"/>
-      <c r="M27" s="47"/>
+      <c r="H27" s="43"/>
+      <c r="I27" s="43"/>
+      <c r="J27" s="43"/>
+      <c r="K27" s="45"/>
+      <c r="L27" s="44"/>
+      <c r="M27" s="44"/>
       <c r="N27" s="1">
         <v>8</v>
       </c>
@@ -2720,19 +2730,19 @@
       <c r="B28" s="41"/>
       <c r="C28" s="41"/>
       <c r="D28" s="41"/>
-      <c r="E28" s="50"/>
+      <c r="E28" s="49"/>
       <c r="F28" s="19">
         <v>6</v>
       </c>
       <c r="G28" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="H28" s="46"/>
-      <c r="I28" s="46"/>
-      <c r="J28" s="46"/>
-      <c r="K28" s="43"/>
-      <c r="L28" s="47"/>
-      <c r="M28" s="47"/>
+      <c r="H28" s="43"/>
+      <c r="I28" s="43"/>
+      <c r="J28" s="43"/>
+      <c r="K28" s="45"/>
+      <c r="L28" s="44"/>
+      <c r="M28" s="44"/>
       <c r="N28" s="1">
         <v>9</v>
       </c>
@@ -2745,19 +2755,19 @@
       <c r="B29" s="41"/>
       <c r="C29" s="41"/>
       <c r="D29" s="41"/>
-      <c r="E29" s="50"/>
+      <c r="E29" s="49"/>
       <c r="F29" s="19">
         <v>6</v>
       </c>
       <c r="G29" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="H29" s="46"/>
-      <c r="I29" s="46"/>
-      <c r="J29" s="46"/>
-      <c r="K29" s="43"/>
-      <c r="L29" s="47"/>
-      <c r="M29" s="47"/>
+      <c r="H29" s="43"/>
+      <c r="I29" s="43"/>
+      <c r="J29" s="43"/>
+      <c r="K29" s="45"/>
+      <c r="L29" s="44"/>
+      <c r="M29" s="44"/>
       <c r="N29" s="1">
         <v>10</v>
       </c>
@@ -2770,19 +2780,19 @@
       <c r="B30" s="41"/>
       <c r="C30" s="41"/>
       <c r="D30" s="41"/>
-      <c r="E30" s="50"/>
+      <c r="E30" s="49"/>
       <c r="F30" s="19">
         <v>6</v>
       </c>
       <c r="G30" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="H30" s="46"/>
-      <c r="I30" s="46"/>
-      <c r="J30" s="46"/>
-      <c r="K30" s="43"/>
-      <c r="L30" s="47"/>
-      <c r="M30" s="47"/>
+      <c r="H30" s="43"/>
+      <c r="I30" s="43"/>
+      <c r="J30" s="43"/>
+      <c r="K30" s="45"/>
+      <c r="L30" s="44"/>
+      <c r="M30" s="44"/>
       <c r="N30" s="1">
         <v>11</v>
       </c>
@@ -2795,18 +2805,18 @@
       <c r="B31" s="41"/>
       <c r="C31" s="41"/>
       <c r="D31" s="41"/>
-      <c r="E31" s="50"/>
+      <c r="E31" s="49"/>
       <c r="F31" s="19">
         <v>6</v>
       </c>
       <c r="G31" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="H31" s="46"/>
-      <c r="I31" s="46"/>
-      <c r="J31" s="46"/>
-      <c r="K31" s="43"/>
-      <c r="L31" s="47"/>
+      <c r="H31" s="43"/>
+      <c r="I31" s="43"/>
+      <c r="J31" s="43"/>
+      <c r="K31" s="45"/>
+      <c r="L31" s="44"/>
       <c r="M31" s="38"/>
       <c r="N31" s="1" t="s">
         <v>180</v>
@@ -2820,18 +2830,18 @@
       <c r="B32" s="41"/>
       <c r="C32" s="41"/>
       <c r="D32" s="41"/>
-      <c r="E32" s="50"/>
+      <c r="E32" s="49"/>
       <c r="F32" s="19">
         <v>6</v>
       </c>
       <c r="G32" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="H32" s="46"/>
-      <c r="I32" s="46"/>
-      <c r="J32" s="46"/>
-      <c r="K32" s="43"/>
-      <c r="L32" s="47"/>
+      <c r="H32" s="43"/>
+      <c r="I32" s="43"/>
+      <c r="J32" s="43"/>
+      <c r="K32" s="45"/>
+      <c r="L32" s="44"/>
       <c r="M32" s="37" t="s">
         <v>162</v>
       </c>
@@ -2847,19 +2857,19 @@
       <c r="B33" s="41"/>
       <c r="C33" s="41"/>
       <c r="D33" s="41"/>
-      <c r="E33" s="50"/>
+      <c r="E33" s="49"/>
       <c r="F33" s="19">
         <v>6</v>
       </c>
       <c r="G33" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="H33" s="46"/>
-      <c r="I33" s="46"/>
-      <c r="J33" s="46"/>
-      <c r="K33" s="43"/>
-      <c r="L33" s="47"/>
-      <c r="M33" s="47"/>
+      <c r="H33" s="43"/>
+      <c r="I33" s="43"/>
+      <c r="J33" s="43"/>
+      <c r="K33" s="45"/>
+      <c r="L33" s="44"/>
+      <c r="M33" s="44"/>
       <c r="N33" s="1">
         <v>1</v>
       </c>
@@ -2872,19 +2882,19 @@
       <c r="B34" s="41"/>
       <c r="C34" s="41"/>
       <c r="D34" s="41"/>
-      <c r="E34" s="50"/>
+      <c r="E34" s="49"/>
       <c r="F34" s="19">
         <v>6</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="H34" s="46"/>
-      <c r="I34" s="46"/>
-      <c r="J34" s="46"/>
-      <c r="K34" s="43"/>
-      <c r="L34" s="47"/>
-      <c r="M34" s="47"/>
+      <c r="H34" s="43"/>
+      <c r="I34" s="43"/>
+      <c r="J34" s="43"/>
+      <c r="K34" s="45"/>
+      <c r="L34" s="44"/>
+      <c r="M34" s="44"/>
       <c r="N34" s="1">
         <v>2</v>
       </c>
@@ -2897,19 +2907,19 @@
       <c r="B35" s="41"/>
       <c r="C35" s="41"/>
       <c r="D35" s="41"/>
-      <c r="E35" s="50"/>
+      <c r="E35" s="49"/>
       <c r="F35" s="19">
         <v>6</v>
       </c>
       <c r="G35" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="H35" s="46"/>
-      <c r="I35" s="46"/>
-      <c r="J35" s="46"/>
-      <c r="K35" s="43"/>
-      <c r="L35" s="47"/>
-      <c r="M35" s="47"/>
+      <c r="H35" s="43"/>
+      <c r="I35" s="43"/>
+      <c r="J35" s="43"/>
+      <c r="K35" s="45"/>
+      <c r="L35" s="44"/>
+      <c r="M35" s="44"/>
       <c r="N35" s="1">
         <v>3</v>
       </c>
@@ -2922,18 +2932,18 @@
       <c r="B36" s="41"/>
       <c r="C36" s="41"/>
       <c r="D36" s="41"/>
-      <c r="E36" s="50"/>
+      <c r="E36" s="49"/>
       <c r="F36" s="19">
         <v>6</v>
       </c>
       <c r="G36" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="H36" s="46"/>
-      <c r="I36" s="46"/>
-      <c r="J36" s="46"/>
-      <c r="K36" s="43"/>
-      <c r="L36" s="47"/>
+      <c r="H36" s="43"/>
+      <c r="I36" s="43"/>
+      <c r="J36" s="43"/>
+      <c r="K36" s="45"/>
+      <c r="L36" s="44"/>
       <c r="M36" s="38"/>
       <c r="N36" s="1" t="s">
         <v>167</v>
@@ -2947,18 +2957,18 @@
       <c r="B37" s="41"/>
       <c r="C37" s="41"/>
       <c r="D37" s="41"/>
-      <c r="E37" s="50"/>
+      <c r="E37" s="49"/>
       <c r="F37" s="19">
         <v>6</v>
       </c>
       <c r="G37" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="H37" s="46"/>
-      <c r="I37" s="46"/>
-      <c r="J37" s="46"/>
-      <c r="K37" s="43"/>
-      <c r="L37" s="47"/>
+      <c r="H37" s="43"/>
+      <c r="I37" s="43"/>
+      <c r="J37" s="43"/>
+      <c r="K37" s="45"/>
+      <c r="L37" s="44"/>
       <c r="M37" s="37" t="s">
         <v>168</v>
       </c>
@@ -2974,19 +2984,19 @@
       <c r="B38" s="41"/>
       <c r="C38" s="41"/>
       <c r="D38" s="41"/>
-      <c r="E38" s="50"/>
+      <c r="E38" s="49"/>
       <c r="F38" s="19">
         <v>6</v>
       </c>
       <c r="G38" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="H38" s="46"/>
-      <c r="I38" s="46"/>
-      <c r="J38" s="46"/>
-      <c r="K38" s="43"/>
-      <c r="L38" s="47"/>
-      <c r="M38" s="47"/>
+      <c r="H38" s="43"/>
+      <c r="I38" s="43"/>
+      <c r="J38" s="43"/>
+      <c r="K38" s="45"/>
+      <c r="L38" s="44"/>
+      <c r="M38" s="44"/>
       <c r="N38" s="1">
         <v>1</v>
       </c>
@@ -2999,19 +3009,19 @@
       <c r="B39" s="41"/>
       <c r="C39" s="41"/>
       <c r="D39" s="41"/>
-      <c r="E39" s="50"/>
+      <c r="E39" s="49"/>
       <c r="F39" s="19">
         <v>6</v>
       </c>
       <c r="G39" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="H39" s="46"/>
-      <c r="I39" s="46"/>
-      <c r="J39" s="46"/>
-      <c r="K39" s="43"/>
-      <c r="L39" s="47"/>
-      <c r="M39" s="47"/>
+      <c r="H39" s="43"/>
+      <c r="I39" s="43"/>
+      <c r="J39" s="43"/>
+      <c r="K39" s="45"/>
+      <c r="L39" s="44"/>
+      <c r="M39" s="44"/>
       <c r="N39" s="1">
         <v>2</v>
       </c>
@@ -3024,19 +3034,19 @@
       <c r="B40" s="41"/>
       <c r="C40" s="41"/>
       <c r="D40" s="41"/>
-      <c r="E40" s="50"/>
+      <c r="E40" s="49"/>
       <c r="F40" s="19">
         <v>6</v>
       </c>
       <c r="G40" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="H40" s="46"/>
-      <c r="I40" s="46"/>
-      <c r="J40" s="46"/>
-      <c r="K40" s="43"/>
-      <c r="L40" s="47"/>
-      <c r="M40" s="47"/>
+      <c r="H40" s="43"/>
+      <c r="I40" s="43"/>
+      <c r="J40" s="43"/>
+      <c r="K40" s="45"/>
+      <c r="L40" s="44"/>
+      <c r="M40" s="44"/>
       <c r="N40" s="1">
         <v>3</v>
       </c>
@@ -3049,19 +3059,19 @@
       <c r="B41" s="41"/>
       <c r="C41" s="41"/>
       <c r="D41" s="41"/>
-      <c r="E41" s="50"/>
+      <c r="E41" s="49"/>
       <c r="F41" s="19">
         <v>6</v>
       </c>
       <c r="G41" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="H41" s="46"/>
-      <c r="I41" s="46"/>
-      <c r="J41" s="46"/>
-      <c r="K41" s="43"/>
-      <c r="L41" s="47"/>
-      <c r="M41" s="47"/>
+      <c r="H41" s="43"/>
+      <c r="I41" s="43"/>
+      <c r="J41" s="43"/>
+      <c r="K41" s="45"/>
+      <c r="L41" s="44"/>
+      <c r="M41" s="44"/>
       <c r="N41" s="1">
         <v>4</v>
       </c>
@@ -3074,19 +3084,19 @@
       <c r="B42" s="41"/>
       <c r="C42" s="41"/>
       <c r="D42" s="41"/>
-      <c r="E42" s="50"/>
+      <c r="E42" s="49"/>
       <c r="F42" s="19">
         <v>6</v>
       </c>
       <c r="G42" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="H42" s="46"/>
-      <c r="I42" s="46"/>
-      <c r="J42" s="46"/>
-      <c r="K42" s="43"/>
-      <c r="L42" s="47"/>
-      <c r="M42" s="47"/>
+      <c r="H42" s="43"/>
+      <c r="I42" s="43"/>
+      <c r="J42" s="43"/>
+      <c r="K42" s="45"/>
+      <c r="L42" s="44"/>
+      <c r="M42" s="44"/>
       <c r="N42" s="1">
         <v>5</v>
       </c>
@@ -3099,18 +3109,18 @@
       <c r="B43" s="41"/>
       <c r="C43" s="41"/>
       <c r="D43" s="41"/>
-      <c r="E43" s="50"/>
+      <c r="E43" s="49"/>
       <c r="F43" s="19">
         <v>6</v>
       </c>
       <c r="G43" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="H43" s="46"/>
-      <c r="I43" s="46"/>
-      <c r="J43" s="46"/>
-      <c r="K43" s="43"/>
-      <c r="L43" s="47"/>
+      <c r="H43" s="43"/>
+      <c r="I43" s="43"/>
+      <c r="J43" s="43"/>
+      <c r="K43" s="45"/>
+      <c r="L43" s="44"/>
       <c r="M43" s="38"/>
       <c r="N43" s="1" t="s">
         <v>175</v>
@@ -3124,18 +3134,18 @@
       <c r="B44" s="41"/>
       <c r="C44" s="41"/>
       <c r="D44" s="41"/>
-      <c r="E44" s="50"/>
+      <c r="E44" s="49"/>
       <c r="F44" s="19">
         <v>8</v>
       </c>
       <c r="G44" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="H44" s="46"/>
-      <c r="I44" s="46"/>
-      <c r="J44" s="46"/>
-      <c r="K44" s="43"/>
-      <c r="L44" s="47"/>
+      <c r="H44" s="43"/>
+      <c r="I44" s="43"/>
+      <c r="J44" s="43"/>
+      <c r="K44" s="45"/>
+      <c r="L44" s="44"/>
       <c r="M44" s="1" t="s">
         <v>176</v>
       </c>
@@ -3149,115 +3159,115 @@
       <c r="B45" s="41"/>
       <c r="C45" s="41"/>
       <c r="D45" s="41"/>
-      <c r="E45" s="50"/>
+      <c r="E45" s="49"/>
       <c r="F45" s="19">
         <v>8</v>
       </c>
       <c r="G45" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="H45" s="46"/>
-      <c r="I45" s="46"/>
-      <c r="J45" s="46"/>
-      <c r="K45" s="43"/>
-      <c r="L45" s="47"/>
+      <c r="H45" s="43"/>
+      <c r="I45" s="43"/>
+      <c r="J45" s="43"/>
+      <c r="K45" s="45"/>
+      <c r="L45" s="44"/>
     </row>
     <row r="46" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="41"/>
       <c r="B46" s="41"/>
       <c r="C46" s="41"/>
       <c r="D46" s="41"/>
-      <c r="E46" s="50"/>
+      <c r="E46" s="49"/>
       <c r="F46" s="19">
         <v>6</v>
       </c>
       <c r="G46" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="H46" s="46"/>
-      <c r="I46" s="46"/>
-      <c r="J46" s="46"/>
-      <c r="K46" s="43"/>
-      <c r="L46" s="47"/>
+      <c r="H46" s="43"/>
+      <c r="I46" s="43"/>
+      <c r="J46" s="43"/>
+      <c r="K46" s="45"/>
+      <c r="L46" s="44"/>
     </row>
     <row r="47" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="41"/>
       <c r="B47" s="41"/>
       <c r="C47" s="41"/>
       <c r="D47" s="41"/>
-      <c r="E47" s="50"/>
+      <c r="E47" s="49"/>
       <c r="F47" s="19">
         <v>6</v>
       </c>
       <c r="G47" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="H47" s="46"/>
-      <c r="I47" s="46"/>
-      <c r="J47" s="46"/>
-      <c r="K47" s="43"/>
-      <c r="L47" s="47"/>
+      <c r="H47" s="43"/>
+      <c r="I47" s="43"/>
+      <c r="J47" s="43"/>
+      <c r="K47" s="45"/>
+      <c r="L47" s="44"/>
     </row>
     <row r="48" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="41"/>
       <c r="B48" s="41"/>
       <c r="C48" s="41"/>
       <c r="D48" s="41"/>
-      <c r="E48" s="50"/>
+      <c r="E48" s="49"/>
       <c r="F48" s="19">
         <v>6</v>
       </c>
       <c r="G48" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="H48" s="46"/>
-      <c r="I48" s="46"/>
-      <c r="J48" s="46"/>
-      <c r="K48" s="43"/>
-      <c r="L48" s="47"/>
+      <c r="H48" s="43"/>
+      <c r="I48" s="43"/>
+      <c r="J48" s="43"/>
+      <c r="K48" s="45"/>
+      <c r="L48" s="44"/>
     </row>
     <row r="49" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="41"/>
       <c r="B49" s="41"/>
       <c r="C49" s="41"/>
       <c r="D49" s="41"/>
-      <c r="E49" s="50"/>
+      <c r="E49" s="49"/>
       <c r="F49" s="19">
         <v>6</v>
       </c>
       <c r="G49" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="H49" s="46"/>
-      <c r="I49" s="46"/>
-      <c r="J49" s="46"/>
-      <c r="K49" s="43"/>
-      <c r="L49" s="47"/>
+      <c r="H49" s="43"/>
+      <c r="I49" s="43"/>
+      <c r="J49" s="43"/>
+      <c r="K49" s="45"/>
+      <c r="L49" s="44"/>
     </row>
     <row r="50" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="41"/>
       <c r="B50" s="41"/>
       <c r="C50" s="41"/>
       <c r="D50" s="41"/>
-      <c r="E50" s="50"/>
+      <c r="E50" s="49"/>
       <c r="F50" s="19">
         <v>6</v>
       </c>
       <c r="G50" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="H50" s="46"/>
-      <c r="I50" s="46"/>
-      <c r="J50" s="46"/>
-      <c r="K50" s="43"/>
-      <c r="L50" s="47"/>
+      <c r="H50" s="43"/>
+      <c r="I50" s="43"/>
+      <c r="J50" s="43"/>
+      <c r="K50" s="45"/>
+      <c r="L50" s="44"/>
     </row>
     <row r="51" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="16"/>
       <c r="B51" s="16"/>
       <c r="C51" s="16"/>
       <c r="D51" s="16"/>
-      <c r="E51" s="51"/>
+      <c r="E51" s="50"/>
       <c r="F51" s="19">
         <v>6</v>
       </c>
@@ -3283,7 +3293,7 @@
       <c r="D52" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E52" s="31" t="s">
+      <c r="E52" s="30" t="s">
         <v>38</v>
       </c>
       <c r="F52" s="1">
@@ -3313,7 +3323,7 @@
       <c r="D53" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E53" s="31"/>
+      <c r="E53" s="30"/>
       <c r="F53" s="1">
         <v>238</v>
       </c>
@@ -3341,7 +3351,7 @@
       <c r="D54" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E54" s="31"/>
+      <c r="E54" s="30"/>
       <c r="F54" s="1">
         <v>238</v>
       </c>
@@ -3369,7 +3379,7 @@
       <c r="D55" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E55" s="31"/>
+      <c r="E55" s="30"/>
       <c r="F55" s="1">
         <v>238</v>
       </c>
@@ -3397,7 +3407,7 @@
       <c r="D56" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E56" s="31"/>
+      <c r="E56" s="30"/>
       <c r="F56" s="1">
         <v>238</v>
       </c>
@@ -3425,7 +3435,7 @@
       <c r="D57" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E57" s="31"/>
+      <c r="E57" s="30"/>
       <c r="F57" s="1">
         <v>238</v>
       </c>
@@ -3453,7 +3463,7 @@
       <c r="D58" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E58" s="31"/>
+      <c r="E58" s="30"/>
       <c r="F58" s="1">
         <v>238</v>
       </c>
@@ -3481,7 +3491,7 @@
       <c r="D59" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E59" s="31"/>
+      <c r="E59" s="30"/>
       <c r="F59" s="1">
         <v>238</v>
       </c>
@@ -3510,7 +3520,7 @@
       <c r="D60" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E60" s="31"/>
+      <c r="E60" s="30"/>
       <c r="F60" s="1">
         <v>238</v>
       </c>
@@ -3538,7 +3548,7 @@
       <c r="D61" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="E61" s="31"/>
+      <c r="E61" s="30"/>
       <c r="F61" s="1">
         <v>238</v>
       </c>
@@ -3567,7 +3577,7 @@
       <c r="D62" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E62" s="31"/>
+      <c r="E62" s="30"/>
       <c r="F62" s="1">
         <v>238</v>
       </c>
@@ -3595,7 +3605,7 @@
       <c r="D63" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E63" s="31"/>
+      <c r="E63" s="30"/>
       <c r="F63" s="1">
         <v>238</v>
       </c>
@@ -3623,7 +3633,7 @@
       <c r="D64" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="E64" s="31"/>
+      <c r="E64" s="30"/>
       <c r="F64" s="1">
         <v>238</v>
       </c>
@@ -3651,7 +3661,7 @@
       <c r="D65" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E65" s="31"/>
+      <c r="E65" s="30"/>
       <c r="F65" s="1">
         <v>238</v>
       </c>
@@ -3680,7 +3690,7 @@
       <c r="D66" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="E66" s="31"/>
+      <c r="E66" s="30"/>
       <c r="F66" s="1">
         <v>238</v>
       </c>
@@ -3708,7 +3718,7 @@
       <c r="D67" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E67" s="31"/>
+      <c r="E67" s="30"/>
       <c r="F67" s="1">
         <v>238</v>
       </c>
@@ -3736,7 +3746,7 @@
       <c r="D68" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E68" s="31"/>
+      <c r="E68" s="30"/>
       <c r="F68" s="1">
         <v>238</v>
       </c>
@@ -3764,7 +3774,7 @@
       <c r="D69" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E69" s="31"/>
+      <c r="E69" s="30"/>
       <c r="F69" s="1">
         <v>238</v>
       </c>
@@ -3792,7 +3802,7 @@
       <c r="D70" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="E70" s="31"/>
+      <c r="E70" s="30"/>
       <c r="F70" s="1">
         <v>238</v>
       </c>
@@ -3820,7 +3830,7 @@
       <c r="D71" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E71" s="31"/>
+      <c r="E71" s="30"/>
       <c r="F71" s="1">
         <v>238</v>
       </c>
@@ -3848,7 +3858,7 @@
       <c r="D72" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E72" s="31"/>
+      <c r="E72" s="30"/>
       <c r="F72" s="1">
         <v>238</v>
       </c>
@@ -3876,7 +3886,7 @@
       <c r="D73" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E73" s="31"/>
+      <c r="E73" s="30"/>
       <c r="F73" s="1">
         <v>238</v>
       </c>
@@ -3904,7 +3914,7 @@
       <c r="D74" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="E74" s="31"/>
+      <c r="E74" s="30"/>
       <c r="F74" s="1">
         <v>238</v>
       </c>
@@ -3932,7 +3942,7 @@
       <c r="D75" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E75" s="31"/>
+      <c r="E75" s="30"/>
       <c r="F75" s="1">
         <v>238</v>
       </c>
@@ -3960,7 +3970,7 @@
       <c r="D76" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E76" s="31"/>
+      <c r="E76" s="30"/>
       <c r="F76" s="1">
         <v>238</v>
       </c>
@@ -3988,7 +3998,7 @@
       <c r="D77" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="E77" s="31"/>
+      <c r="E77" s="30"/>
       <c r="F77" s="1">
         <v>238</v>
       </c>
@@ -4016,7 +4026,7 @@
       <c r="D78" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="E78" s="31"/>
+      <c r="E78" s="30"/>
       <c r="F78" s="1">
         <v>238</v>
       </c>
@@ -4044,7 +4054,7 @@
       <c r="D79" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E79" s="31"/>
+      <c r="E79" s="30"/>
       <c r="F79" s="1">
         <v>238</v>
       </c>
@@ -4072,7 +4082,7 @@
       <c r="D80" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="E80" s="31"/>
+      <c r="E80" s="30"/>
       <c r="F80" s="1">
         <v>238</v>
       </c>
@@ -4100,7 +4110,7 @@
       <c r="D81" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="E81" s="31"/>
+      <c r="E81" s="30"/>
       <c r="F81" s="1">
         <v>238</v>
       </c>
@@ -4128,7 +4138,7 @@
       <c r="D82" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="E82" s="31"/>
+      <c r="E82" s="30"/>
       <c r="F82" s="1">
         <v>238</v>
       </c>
@@ -4156,7 +4166,7 @@
       <c r="D83" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E83" s="31"/>
+      <c r="E83" s="30"/>
       <c r="F83" s="1">
         <v>238</v>
       </c>
@@ -4184,7 +4194,7 @@
       <c r="D84" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="E84" s="31"/>
+      <c r="E84" s="30"/>
       <c r="F84" s="1">
         <v>238</v>
       </c>
@@ -4212,7 +4222,7 @@
       <c r="D85" s="1">
         <v>23</v>
       </c>
-      <c r="E85" s="31"/>
+      <c r="E85" s="30"/>
       <c r="F85" s="1">
         <v>238</v>
       </c>
@@ -4240,7 +4250,7 @@
       <c r="D86" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="E86" s="31"/>
+      <c r="E86" s="30"/>
       <c r="F86" s="1">
         <v>238</v>
       </c>
@@ -4268,7 +4278,7 @@
       <c r="D87" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E87" s="31"/>
+      <c r="E87" s="30"/>
       <c r="F87" s="1">
         <v>238</v>
       </c>
@@ -4313,12 +4323,18 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="D18:D50"/>
-    <mergeCell ref="J18:J50"/>
-    <mergeCell ref="L18:L50"/>
-    <mergeCell ref="M19:M31"/>
-    <mergeCell ref="M32:M36"/>
-    <mergeCell ref="M37:M43"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:J3"/>
+    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="A4:A16"/>
+    <mergeCell ref="B4:B16"/>
+    <mergeCell ref="C4:C16"/>
+    <mergeCell ref="C18:C50"/>
+    <mergeCell ref="B18:B50"/>
+    <mergeCell ref="A18:A50"/>
     <mergeCell ref="E52:E87"/>
     <mergeCell ref="K5:K16"/>
     <mergeCell ref="K2:K3"/>
@@ -4330,18 +4346,12 @@
     <mergeCell ref="I4:I16"/>
     <mergeCell ref="E5:E16"/>
     <mergeCell ref="E18:E51"/>
-    <mergeCell ref="A4:A16"/>
-    <mergeCell ref="B4:B16"/>
-    <mergeCell ref="C4:C16"/>
-    <mergeCell ref="C18:C50"/>
-    <mergeCell ref="B18:B50"/>
-    <mergeCell ref="A18:A50"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:J3"/>
-    <mergeCell ref="G2:G3"/>
+    <mergeCell ref="D18:D50"/>
+    <mergeCell ref="J18:J50"/>
+    <mergeCell ref="L18:L50"/>
+    <mergeCell ref="M19:M31"/>
+    <mergeCell ref="M32:M36"/>
+    <mergeCell ref="M37:M43"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A4:E4 K60 A18:E18 D5:D17 A2:K2 K52:K56 A3:F3 H3:J3 K17 K4:K5 E52 D52:D84 D86:D88 A52:C88 K62 J4:J18 J52:J88">
